--- a/database/event/4328/event_4328_evp_summary.xlsx
+++ b/database/event/4328/event_4328_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.7206</v>
+        <v>5.3439</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0751</v>
+        <v>1.2171</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4857</v>
+        <v>1.6851</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7206</v>
+        <v>5.3439</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5247</v>
+        <v>3.148</v>
       </c>
       <c r="G2" t="n">
         <v>2.1959</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5247</v>
+        <v>3.148</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5247</v>
+        <v>3.148</v>
       </c>
       <c r="J2" t="n">
         <v>2.1959</v>
@@ -529,7 +529,7 @@
         <v>54</v>
       </c>
       <c r="M2" t="n">
-        <v>4.7206</v>
+        <v>5.3439</v>
       </c>
       <c r="N2" t="n">
         <v>181</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.9283</v>
+        <v>3.4786</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6669</v>
+        <v>0.7923</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9283</v>
+        <v>3.4786</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9283</v>
+        <v>3.4786</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9283</v>
+        <v>3.4786</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9283</v>
+        <v>3.4786</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9283</v>
+        <v>3.4786</v>
       </c>
       <c r="N3" t="n">
         <v>137</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.6804</v>
+        <v>3.3398</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6105</v>
+        <v>0.7607</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6615</v>
+        <v>0.8867</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6804</v>
+        <v>3.3398</v>
       </c>
       <c r="F4" t="n">
-        <v>2.293</v>
+        <v>2.8304</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3874</v>
+        <v>0.5094</v>
       </c>
       <c r="H4" t="n">
-        <v>2.293</v>
+        <v>2.8304</v>
       </c>
       <c r="I4" t="n">
-        <v>2.293</v>
+        <v>2.8304</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3874</v>
+        <v>0.5094</v>
       </c>
       <c r="K4" t="n">
         <v>132</v>
@@ -621,7 +621,7 @@
         <v>54</v>
       </c>
       <c r="M4" t="n">
-        <v>2.6804</v>
+        <v>3.3398</v>
       </c>
       <c r="N4" t="n">
         <v>186</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.5249</v>
+        <v>3.2828</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.7477</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5986</v>
+        <v>0.864</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5249</v>
+        <v>3.2828</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0155</v>
+        <v>4.2667</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5094</v>
+        <v>-0.9839</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0155</v>
+        <v>4.3871</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0155</v>
+        <v>4.3871</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5094</v>
+        <v>-0.9839</v>
       </c>
       <c r="K5" t="n">
         <v>132</v>
@@ -667,7 +667,7 @@
         <v>54</v>
       </c>
       <c r="M5" t="n">
-        <v>2.5249</v>
+        <v>3.4032</v>
       </c>
       <c r="N5" t="n">
         <v>186</v>
@@ -676,357 +676,357 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.1433</v>
+        <v>3.2725</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4882</v>
+        <v>0.7453</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4445</v>
+        <v>0.8599</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1433</v>
+        <v>3.2725</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1433</v>
+        <v>2.8851</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.3874</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1433</v>
+        <v>2.8851</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1433</v>
+        <v>2.8851</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.3874</v>
       </c>
       <c r="K6" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M6" t="n">
-        <v>2.1433</v>
+        <v>3.2725</v>
       </c>
       <c r="N6" t="n">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.8788</v>
+        <v>2.8066</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4279</v>
+        <v>0.6392</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3376</v>
+        <v>0.6742</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8788</v>
+        <v>2.8066</v>
       </c>
       <c r="F7" t="n">
-        <v>1.358</v>
+        <v>2.8066</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5208</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.358</v>
+        <v>2.8066</v>
       </c>
       <c r="I7" t="n">
-        <v>1.358</v>
+        <v>2.8066</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5208</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="L7" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8788</v>
+        <v>2.8066</v>
       </c>
       <c r="N7" t="n">
-        <v>181</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.7846</v>
+        <v>2.3418</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4065</v>
+        <v>0.5334</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2996</v>
+        <v>0.4891</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7846</v>
+        <v>2.3418</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7685</v>
+        <v>2.3418</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9839</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7685</v>
+        <v>2.3418</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7685</v>
+        <v>2.3418</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9839</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="L8" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7846</v>
+        <v>2.3418</v>
       </c>
       <c r="N8" t="n">
-        <v>186</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.7773</v>
+        <v>2.2961</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4048</v>
+        <v>0.523</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2966</v>
+        <v>0.4709</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7773</v>
+        <v>2.2961</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7773</v>
+        <v>1.7753</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.5208</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7773</v>
+        <v>1.7753</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7773</v>
+        <v>1.7753</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.5208</v>
       </c>
       <c r="K9" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7773</v>
+        <v>2.2961</v>
       </c>
       <c r="N9" t="n">
-        <v>120</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>xseveN</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.3592</v>
+        <v>2.1144</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3096</v>
+        <v>0.4816</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1277</v>
+        <v>0.3985</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3592</v>
+        <v>2.1144</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4087</v>
+        <v>2.1144</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9505</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4087</v>
+        <v>2.1144</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4087</v>
+        <v>2.1144</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9505</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="L10" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3592</v>
+        <v>2.1144</v>
       </c>
       <c r="N10" t="n">
-        <v>181</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3463</v>
+        <v>1.8782</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3066</v>
+        <v>0.4278</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1225</v>
+        <v>0.3044</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3463</v>
+        <v>1.8782</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3463</v>
+        <v>2.483</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0.6048</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3463</v>
+        <v>2.483</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3463</v>
+        <v>2.483</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.6048</v>
       </c>
       <c r="K11" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3463</v>
+        <v>1.8782</v>
       </c>
       <c r="N11" t="n">
-        <v>117</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>roman</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.1361</v>
+        <v>1.5694</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2588</v>
+        <v>0.3574</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0376</v>
+        <v>0.1813</v>
       </c>
       <c r="E12" t="n">
-        <v>1.1361</v>
+        <v>1.5694</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1361</v>
+        <v>1.5694</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1361</v>
+        <v>1.5694</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1361</v>
+        <v>1.5694</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1361</v>
+        <v>1.5694</v>
       </c>
       <c r="N12" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>xseveN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9198</v>
+        <v>1.3592</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2095</v>
+        <v>0.3096</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0498</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9198</v>
+        <v>1.3592</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5246</v>
+        <v>0.4087</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6048</v>
+        <v>0.9505</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5246</v>
+        <v>0.4087</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5246</v>
+        <v>0.4087</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6048</v>
+        <v>0.9505</v>
       </c>
       <c r="K13" t="n">
         <v>127</v>
@@ -1035,7 +1035,7 @@
         <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9198</v>
+        <v>1.3592</v>
       </c>
       <c r="N13" t="n">
         <v>181</v>
@@ -1044,78 +1044,78 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>roman</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6866</v>
+        <v>1.1373</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1564</v>
+        <v>0.259</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.144</v>
+        <v>0.0092</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6866</v>
+        <v>1.1373</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6866</v>
+        <v>1.1373</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6866</v>
+        <v>1.1373</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6866</v>
+        <v>1.1373</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6866</v>
+        <v>1.1373</v>
       </c>
       <c r="N14" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6387</v>
+        <v>1.0285</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1455</v>
+        <v>0.2342</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1633</v>
+        <v>-0.0342</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6387</v>
+        <v>1.0285</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6387</v>
+        <v>1.0285</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6387</v>
+        <v>1.0285</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6387</v>
+        <v>1.0285</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6387</v>
+        <v>1.0285</v>
       </c>
       <c r="N15" t="n">
         <v>120</v>
@@ -1136,47 +1136,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.9143</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1289</v>
+        <v>0.2082</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1927</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.9143</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4338</v>
+        <v>0.9143</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1322</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4338</v>
+        <v>0.9143</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4338</v>
+        <v>0.9143</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1322</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="L16" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5660000000000001</v>
+        <v>0.9143</v>
       </c>
       <c r="N16" t="n">
-        <v>181</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3352</v>
+        <v>0.8195</v>
       </c>
       <c r="C17" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.1866</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2859</v>
+        <v>-0.1174</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3352</v>
+        <v>0.8195</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3352</v>
+        <v>0.8195</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3352</v>
+        <v>0.8195</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3352</v>
+        <v>0.8195</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3352</v>
+        <v>0.8195</v>
       </c>
       <c r="N17" t="n">
         <v>117</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1976</v>
+        <v>0.599</v>
       </c>
       <c r="C18" t="n">
-        <v>0.045</v>
+        <v>0.1364</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3415</v>
+        <v>-0.2053</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1976</v>
+        <v>0.599</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1976</v>
+        <v>0.4668</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.1322</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1976</v>
+        <v>0.4668</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1976</v>
+        <v>0.4668</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.1322</v>
       </c>
       <c r="K18" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1976</v>
+        <v>0.599</v>
       </c>
       <c r="N18" t="n">
-        <v>117</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1581</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>0.036</v>
+        <v>0.1259</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3575</v>
+        <v>-0.2236</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1581</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1581</v>
+        <v>1.5529</v>
       </c>
       <c r="G19" t="n">
         <v>-1</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1581</v>
+        <v>1.5529</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1581</v>
+        <v>1.5529</v>
       </c>
       <c r="J19" t="n">
         <v>-1</v>
@@ -1311,7 +1311,7 @@
         <v>54</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1580999999999999</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="N19" t="n">
         <v>186</v>
@@ -1320,32 +1320,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0842</v>
+        <v>0.2383</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0192</v>
+        <v>0.0543</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3873</v>
+        <v>-0.349</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0842</v>
+        <v>0.2383</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0842</v>
+        <v>0.2383</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0842</v>
+        <v>0.2383</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0842</v>
+        <v>0.2383</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0842</v>
+        <v>0.2383</v>
       </c>
       <c r="N20" t="n">
         <v>117</v>
@@ -1366,32 +1366,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>MUTiRiS</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2354</v>
+        <v>-0.0031</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0536</v>
+        <v>-0.0007</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5165</v>
+        <v>-0.4451</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2354</v>
+        <v>-0.0031</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2354</v>
+        <v>-0.0031</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2354</v>
+        <v>-0.0031</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2354</v>
+        <v>-0.0031</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2354</v>
+        <v>-0.0031</v>
       </c>
       <c r="N21" t="n">
         <v>123</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.3243</v>
+        <v>-0.1549</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0353</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5524</v>
+        <v>-0.5056</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3243</v>
+        <v>-0.1549</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3243</v>
+        <v>-0.1549</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3243</v>
+        <v>-0.1549</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3243</v>
+        <v>-0.1549</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3243</v>
+        <v>-0.1549</v>
       </c>
       <c r="N22" t="n">
         <v>123</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4076</v>
+        <v>-0.2354</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.0536</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.586</v>
+        <v>-0.5377</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4076</v>
+        <v>-0.2354</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4076</v>
+        <v>-0.2354</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4076</v>
+        <v>-0.2354</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4076</v>
+        <v>-0.2354</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4076</v>
+        <v>-0.2354</v>
       </c>
       <c r="N23" t="n">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.4285</v>
+        <v>-0.3425</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.078</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5945</v>
+        <v>-0.5804</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4285</v>
+        <v>-0.3425</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3654</v>
+        <v>-0.2794</v>
       </c>
       <c r="G24" t="n">
         <v>-0.0631</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3654</v>
+        <v>-0.2794</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3654</v>
+        <v>-0.2794</v>
       </c>
       <c r="J24" t="n">
         <v>-0.0631</v>
@@ -1541,7 +1541,7 @@
         <v>54</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4285</v>
+        <v>-0.3425</v>
       </c>
       <c r="N24" t="n">
         <v>186</v>
@@ -1550,32 +1550,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.7164</v>
+        <v>-0.3776</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1632</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7108</v>
+        <v>-0.5943000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.7164</v>
+        <v>-0.3776</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7164</v>
+        <v>-0.3776</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7164</v>
+        <v>-0.3776</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7164</v>
+        <v>-0.3776</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.7164</v>
+        <v>-0.3776</v>
       </c>
       <c r="N25" t="n">
         <v>137</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MUTiRiS</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.9338</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.2127</v>
+        <v>-0.1491</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7986</v>
+        <v>-0.7047</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.9338</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9338</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.9338</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9338</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.9338</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.0195</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2322</v>
+        <v>-0.1824</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.763</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.0195</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.0195</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.0195</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.0195</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.0195</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>120</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.5001</v>
+        <v>-1.3875</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.3417</v>
+        <v>-0.316</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.0274</v>
+        <v>-0.9967</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.5001</v>
+        <v>-1.3875</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.5001</v>
+        <v>-1.3875</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.5001</v>
+        <v>-1.3875</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.5001</v>
+        <v>-1.3875</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.5001</v>
+        <v>-1.3875</v>
       </c>
       <c r="N28" t="n">
         <v>123</v>
@@ -1744,7 +1744,7 @@
         <v>-0.3944</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.1208</v>
+        <v>-1.1337</v>
       </c>
       <c r="E29" t="n">
         <v>-1.7315</v>
@@ -1790,7 +1790,7 @@
         <v>-0.4953</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.2999</v>
+        <v>-1.3104</v>
       </c>
       <c r="E30" t="n">
         <v>-2.1748</v>
@@ -1836,7 +1836,7 @@
         <v>-0.729</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.7144</v>
+        <v>-1.7191</v>
       </c>
       <c r="E31" t="n">
         <v>-3.2007</v>

--- a/database/event/4328/event_4328_evp_summary.xlsx
+++ b/database/event/4328/event_4328_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.3439</v>
+        <v>4.9371</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2171</v>
+        <v>1.1245</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6851</v>
+        <v>1.5908</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3439</v>
+        <v>4.9371</v>
       </c>
       <c r="F2" t="n">
-        <v>3.148</v>
+        <v>2.9085</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1959</v>
+        <v>2.0286</v>
       </c>
       <c r="H2" t="n">
-        <v>3.148</v>
+        <v>3.0268</v>
       </c>
       <c r="I2" t="n">
-        <v>3.148</v>
+        <v>3.0268</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1959</v>
+        <v>2.0286</v>
       </c>
       <c r="K2" t="n">
         <v>127</v>
@@ -529,7 +529,7 @@
         <v>54</v>
       </c>
       <c r="M2" t="n">
-        <v>5.3439</v>
+        <v>5.055400000000001</v>
       </c>
       <c r="N2" t="n">
         <v>181</v>
@@ -538,81 +538,81 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.4786</v>
+        <v>3.4415</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7923</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9157</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4786</v>
+        <v>3.4415</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4786</v>
+        <v>2.9135</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.528</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4786</v>
+        <v>3.0378</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4786</v>
+        <v>3.0378</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.528</v>
       </c>
       <c r="K3" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4786</v>
+        <v>3.5658</v>
       </c>
       <c r="N3" t="n">
-        <v>137</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.3398</v>
+        <v>3.4006</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7607</v>
+        <v>0.7745</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8867</v>
+        <v>0.8972</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3398</v>
+        <v>3.4006</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8304</v>
+        <v>2.8489</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5094</v>
+        <v>0.5517</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8304</v>
+        <v>2.896</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8304</v>
+        <v>2.896</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5094</v>
+        <v>0.5517</v>
       </c>
       <c r="K4" t="n">
         <v>132</v>
@@ -621,7 +621,7 @@
         <v>54</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3398</v>
+        <v>3.4477</v>
       </c>
       <c r="N4" t="n">
         <v>186</v>
@@ -630,81 +630,81 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2828</v>
+        <v>3.238</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7477</v>
+        <v>0.7375</v>
       </c>
       <c r="D5" t="n">
-        <v>0.864</v>
+        <v>0.8238</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2828</v>
+        <v>3.238</v>
       </c>
       <c r="F5" t="n">
-        <v>4.2667</v>
+        <v>3.238</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9839</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3871</v>
+        <v>3.7503</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3871</v>
+        <v>3.7503</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9839</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="L5" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4032</v>
+        <v>3.7503</v>
       </c>
       <c r="N5" t="n">
-        <v>186</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.2725</v>
+        <v>2.8633</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7453</v>
+        <v>0.6521</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8599</v>
+        <v>0.6546</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2725</v>
+        <v>2.8633</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8851</v>
+        <v>3.5023</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3874</v>
+        <v>-0.639</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8851</v>
+        <v>4.3307</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8851</v>
+        <v>4.3307</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3874</v>
+        <v>-0.639</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -713,7 +713,7 @@
         <v>54</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2725</v>
+        <v>3.6917</v>
       </c>
       <c r="N6" t="n">
         <v>186</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8066</v>
+        <v>2.8475</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6392</v>
+        <v>0.6485</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6742</v>
+        <v>0.6475</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8066</v>
+        <v>2.8475</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8066</v>
+        <v>2.8475</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8066</v>
+        <v>2.8928</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8066</v>
+        <v>2.8928</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8066</v>
+        <v>2.8928</v>
       </c>
       <c r="N7" t="n">
         <v>117</v>
@@ -768,139 +768,139 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3418</v>
+        <v>2.4389</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5334</v>
+        <v>0.5555</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4891</v>
+        <v>0.463</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3418</v>
+        <v>2.4389</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3418</v>
+        <v>1.851</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.5879</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3418</v>
+        <v>1.851</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3418</v>
+        <v>1.851</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.5879</v>
       </c>
       <c r="K8" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3418</v>
+        <v>2.4389</v>
       </c>
       <c r="N8" t="n">
-        <v>117</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2961</v>
+        <v>2.346</v>
       </c>
       <c r="C9" t="n">
-        <v>0.523</v>
+        <v>0.5343</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4709</v>
+        <v>0.4211</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2961</v>
+        <v>2.346</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7753</v>
+        <v>2.346</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5208</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7753</v>
+        <v>2.346</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7753</v>
+        <v>2.346</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5208</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="L9" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2961</v>
+        <v>2.346</v>
       </c>
       <c r="N9" t="n">
-        <v>181</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1144</v>
+        <v>2.3026</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4816</v>
+        <v>0.5244</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3985</v>
+        <v>0.4015</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1144</v>
+        <v>2.3026</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1144</v>
+        <v>2.3026</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1144</v>
+        <v>2.3026</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1144</v>
+        <v>2.3026</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1144</v>
+        <v>2.3026</v>
       </c>
       <c r="N10" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8782</v>
+        <v>2.0962</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4278</v>
+        <v>0.4774</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3044</v>
+        <v>0.3083</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8782</v>
+        <v>2.0962</v>
       </c>
       <c r="F11" t="n">
-        <v>2.483</v>
+        <v>2.5737</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6048</v>
+        <v>-0.4775</v>
       </c>
       <c r="H11" t="n">
-        <v>2.483</v>
+        <v>2.5737</v>
       </c>
       <c r="I11" t="n">
-        <v>2.483</v>
+        <v>2.5737</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6048</v>
+        <v>-0.4775</v>
       </c>
       <c r="K11" t="n">
         <v>127</v>
@@ -943,7 +943,7 @@
         <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8782</v>
+        <v>2.0962</v>
       </c>
       <c r="N11" t="n">
         <v>181</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5694</v>
+        <v>1.5996</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3574</v>
+        <v>0.3643</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1813</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5694</v>
+        <v>1.5996</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5694</v>
+        <v>1.5996</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5694</v>
+        <v>1.5996</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5694</v>
+        <v>1.5996</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5694</v>
+        <v>1.5996</v>
       </c>
       <c r="N12" t="n">
         <v>120</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>xseveN</t>
+          <t>roman</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.3592</v>
+        <v>1.5586</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3096</v>
+        <v>0.355</v>
       </c>
       <c r="D13" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3592</v>
+        <v>1.5586</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4087</v>
+        <v>1.5586</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9505</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4087</v>
+        <v>1.5586</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4087</v>
+        <v>1.5586</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9505</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L13" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3592</v>
+        <v>1.5586</v>
       </c>
       <c r="N13" t="n">
-        <v>181</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>roman</t>
+          <t>xseveN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1373</v>
+        <v>1.4833</v>
       </c>
       <c r="C14" t="n">
-        <v>0.259</v>
+        <v>0.3378</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0092</v>
+        <v>0.0316</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1373</v>
+        <v>1.4833</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1373</v>
+        <v>0.5337</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.9496</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1373</v>
+        <v>0.5337</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1373</v>
+        <v>0.5337</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.9496</v>
       </c>
       <c r="K14" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1373</v>
+        <v>1.4833</v>
       </c>
       <c r="N14" t="n">
-        <v>123</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.0285</v>
+        <v>1.325</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2342</v>
+        <v>0.3018</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0342</v>
+        <v>-0.0398</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0285</v>
+        <v>1.325</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0285</v>
+        <v>1.325</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0285</v>
+        <v>1.325</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0285</v>
+        <v>1.325</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0285</v>
+        <v>1.325</v>
       </c>
       <c r="N15" t="n">
         <v>120</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9143</v>
+        <v>1.2312</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2082</v>
+        <v>0.2804</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0822</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9143</v>
+        <v>1.2312</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9143</v>
+        <v>1.2312</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9143</v>
+        <v>1.2312</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9143</v>
+        <v>1.2312</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9143</v>
+        <v>1.2312</v>
       </c>
       <c r="N16" t="n">
         <v>117</v>
@@ -1182,139 +1182,139 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8195</v>
+        <v>1.133</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1866</v>
+        <v>0.258</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1174</v>
+        <v>-0.1265</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8195</v>
+        <v>1.133</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8195</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8195</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8195</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="K17" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8195</v>
+        <v>1.133</v>
       </c>
       <c r="N17" t="n">
-        <v>117</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.599</v>
+        <v>1.0883</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1364</v>
+        <v>0.2479</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2053</v>
+        <v>-0.1467</v>
       </c>
       <c r="E18" t="n">
-        <v>0.599</v>
+        <v>1.0883</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4668</v>
+        <v>1.8308</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1322</v>
+        <v>-0.7425</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4668</v>
+        <v>1.8308</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4668</v>
+        <v>1.8308</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1322</v>
+        <v>-0.7425</v>
       </c>
       <c r="K18" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="L18" t="n">
         <v>54</v>
       </c>
       <c r="M18" t="n">
-        <v>0.599</v>
+        <v>1.0883</v>
       </c>
       <c r="N18" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5528999999999999</v>
+        <v>1.067</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1259</v>
+        <v>0.243</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2236</v>
+        <v>-0.1563</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5528999999999999</v>
+        <v>1.067</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5529</v>
+        <v>1.067</v>
       </c>
       <c r="G19" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5529</v>
+        <v>1.067</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5529</v>
+        <v>1.067</v>
       </c>
       <c r="J19" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="L19" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5528999999999999</v>
+        <v>1.067</v>
       </c>
       <c r="N19" t="n">
-        <v>186</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2383</v>
+        <v>0.827</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0543</v>
+        <v>0.1884</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.349</v>
+        <v>-0.2647</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2383</v>
+        <v>0.827</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2383</v>
+        <v>0.827</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2383</v>
+        <v>0.827</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2383</v>
+        <v>0.827</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2383</v>
+        <v>0.827</v>
       </c>
       <c r="N20" t="n">
         <v>117</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.0031</v>
+        <v>0.496</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0007</v>
+        <v>0.113</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4451</v>
+        <v>-0.4141</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0031</v>
+        <v>0.496</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0031</v>
+        <v>0.496</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0031</v>
+        <v>0.496</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0031</v>
+        <v>0.496</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0031</v>
+        <v>0.496</v>
       </c>
       <c r="N21" t="n">
         <v>123</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1549</v>
+        <v>0.2682</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0353</v>
+        <v>0.0611</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5056</v>
+        <v>-0.5169</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1549</v>
+        <v>0.2682</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1549</v>
+        <v>0.2682</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1549</v>
+        <v>0.2682</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1549</v>
+        <v>0.2682</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1549</v>
+        <v>0.2682</v>
       </c>
       <c r="N22" t="n">
         <v>123</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.2354</v>
+        <v>0.1264</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0536</v>
+        <v>0.0288</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5377</v>
+        <v>-0.581</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2354</v>
+        <v>0.1264</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2354</v>
+        <v>0.1264</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2354</v>
+        <v>0.1264</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2354</v>
+        <v>0.1264</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2354</v>
+        <v>0.1264</v>
       </c>
       <c r="N23" t="n">
         <v>123</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3425</v>
+        <v>0.0736</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.078</v>
+        <v>0.0168</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5804</v>
+        <v>-0.6048</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3425</v>
+        <v>0.0736</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2794</v>
+        <v>0.1363</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0631</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2794</v>
+        <v>0.1363</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2794</v>
+        <v>0.1363</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0631</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>132</v>
@@ -1541,7 +1541,7 @@
         <v>54</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3425</v>
+        <v>0.0736</v>
       </c>
       <c r="N24" t="n">
         <v>186</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3776</v>
+        <v>-0.0584</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.0133</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.6644</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3776</v>
+        <v>-0.0584</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3776</v>
+        <v>-0.0584</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3776</v>
+        <v>-0.0584</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3776</v>
+        <v>-0.0584</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3776</v>
+        <v>-0.0584</v>
       </c>
       <c r="N25" t="n">
         <v>137</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.6546999999999999</v>
+        <v>-0.1391</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1491</v>
+        <v>-0.0317</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7047</v>
+        <v>-0.7008</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6546999999999999</v>
+        <v>-0.1391</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6546999999999999</v>
+        <v>-0.1391</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.6546999999999999</v>
+        <v>-0.1391</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6546999999999999</v>
+        <v>-0.1391</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.6546999999999999</v>
+        <v>-0.1391</v>
       </c>
       <c r="N26" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.2169</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1824</v>
+        <v>-0.0494</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.763</v>
+        <v>-0.7359</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.2169</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.2169</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.2169</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.2169</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.2169</v>
       </c>
       <c r="N27" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.3875</v>
+        <v>-0.5132</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.316</v>
+        <v>-0.1169</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.9967</v>
+        <v>-0.8697</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.3875</v>
+        <v>-0.5132</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.3875</v>
+        <v>-0.5132</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.3875</v>
+        <v>-0.5132</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.3875</v>
+        <v>-0.5132</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.3875</v>
+        <v>-0.5132</v>
       </c>
       <c r="N28" t="n">
         <v>123</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.7315</v>
+        <v>-1.3849</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3944</v>
+        <v>-0.3154</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.1337</v>
+        <v>-1.2632</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.7315</v>
+        <v>-1.3849</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.7315</v>
+        <v>-1.3849</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.7315</v>
+        <v>-1.3849</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.7315</v>
+        <v>-1.3849</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.7315</v>
+        <v>-1.3849</v>
       </c>
       <c r="N29" t="n">
         <v>120</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.1748</v>
+        <v>-1.5432</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.4953</v>
+        <v>-0.3515</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.3104</v>
+        <v>-1.3347</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.1748</v>
+        <v>-1.5432</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.1748</v>
+        <v>-1.5432</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.1748</v>
+        <v>-1.5432</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.1748</v>
+        <v>-1.5432</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.1748</v>
+        <v>-1.5432</v>
       </c>
       <c r="N30" t="n">
         <v>137</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-3.2007</v>
+        <v>-2.303</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.729</v>
+        <v>-0.5245</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.7191</v>
+        <v>-1.6777</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.2007</v>
+        <v>-2.303</v>
       </c>
       <c r="F31" t="n">
-        <v>-3.2007</v>
+        <v>-2.303</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-3.2007</v>
+        <v>-2.303</v>
       </c>
       <c r="I31" t="n">
-        <v>-3.2007</v>
+        <v>-2.303</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-3.2007</v>
+        <v>-2.303</v>
       </c>
       <c r="N31" t="n">
         <v>137</v>
@@ -1969,10 +1969,10 @@
         <v>1.06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2178</v>
+        <v>0.2106</v>
       </c>
       <c r="J2" t="n">
-        <v>5.445</v>
+        <v>5.265</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>0.91</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1239</v>
+        <v>-0.107</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.0975</v>
+        <v>-2.675</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.87</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1972</v>
+        <v>-0.1508</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.93</v>
+        <v>-3.77</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.7</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4842</v>
+        <v>-0.3167</v>
       </c>
       <c r="J5" t="n">
-        <v>-12.105</v>
+        <v>-7.9175</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.68</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5119</v>
+        <v>-0.3357</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.7975</v>
+        <v>-8.3925</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.59</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3771</v>
+        <v>1.244</v>
       </c>
       <c r="J7" t="n">
-        <v>34.4275</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.29</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7405</v>
+        <v>0.7599</v>
       </c>
       <c r="J8" t="n">
-        <v>18.5125</v>
+        <v>18.9975</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>1.29</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7405</v>
+        <v>0.7599</v>
       </c>
       <c r="J9" t="n">
-        <v>18.5125</v>
+        <v>18.9975</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>1.03</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0015</v>
+        <v>0.0736</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0375</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>1.02</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0388</v>
+        <v>0.0365</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.97</v>
+        <v>0.9125</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.34</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5846</v>
+        <v>0.7025</v>
       </c>
       <c r="J12" t="n">
-        <v>16.9534</v>
+        <v>20.3725</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2916</v>
+        <v>0.3174</v>
       </c>
       <c r="J13" t="n">
-        <v>8.4564</v>
+        <v>9.204599999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0608</v>
+        <v>0.0443</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7632</v>
+        <v>1.2847</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.71</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4997</v>
+        <v>-0.3223</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.4913</v>
+        <v>-9.3467</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.62</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.4068</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.8466</v>
+        <v>-11.7972</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.27</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8188</v>
+        <v>0.7846</v>
       </c>
       <c r="J17" t="n">
-        <v>23.7452</v>
+        <v>22.7534</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.21</v>
+        <v>0.1897</v>
       </c>
       <c r="J18" t="n">
-        <v>6.09</v>
+        <v>5.5013</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>0.171</v>
+        <v>0.1575</v>
       </c>
       <c r="J19" t="n">
-        <v>4.959</v>
+        <v>4.5675</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2197</v>
+        <v>-0.172</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.3713</v>
+        <v>-4.988</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6032999999999999</v>
+        <v>-0.5511</v>
       </c>
       <c r="J21" t="n">
-        <v>-17.4957</v>
+        <v>-15.9819</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.28</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7748</v>
+        <v>0.7624</v>
       </c>
       <c r="J22" t="n">
-        <v>23.244</v>
+        <v>22.872</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.24</v>
       </c>
       <c r="I23" t="n">
-        <v>0.678</v>
+        <v>0.667</v>
       </c>
       <c r="J23" t="n">
-        <v>20.34</v>
+        <v>20.01</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.22</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6187</v>
       </c>
       <c r="J24" t="n">
-        <v>18.825</v>
+        <v>18.561</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.13</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3572</v>
+        <v>0.3953</v>
       </c>
       <c r="J25" t="n">
-        <v>10.716</v>
+        <v>11.859</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5411</v>
+        <v>-0.4752</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.233</v>
+        <v>-14.256</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.06</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1742</v>
+        <v>0.1729</v>
       </c>
       <c r="J27" t="n">
-        <v>5.226</v>
+        <v>5.187</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1549</v>
+        <v>0.15</v>
       </c>
       <c r="J28" t="n">
-        <v>4.647</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0067</v>
+        <v>-0.017</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.201</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.92</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1743</v>
+        <v>-0.1069</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.229</v>
+        <v>-3.207</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4436</v>
+        <v>-0.2828</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.308</v>
+        <v>-8.484</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.49</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1552</v>
+        <v>1.1083</v>
       </c>
       <c r="J32" t="n">
-        <v>31.1904</v>
+        <v>29.9241</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8035</v>
+        <v>0.8386</v>
       </c>
       <c r="J33" t="n">
-        <v>21.6945</v>
+        <v>22.6422</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1.28</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6614</v>
+        <v>0.7298</v>
       </c>
       <c r="J34" t="n">
-        <v>17.8578</v>
+        <v>19.7046</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>1.28</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6614</v>
+        <v>0.7298</v>
       </c>
       <c r="J35" t="n">
-        <v>17.8578</v>
+        <v>19.7046</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>1.1</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1961</v>
+        <v>0.28</v>
       </c>
       <c r="J36" t="n">
-        <v>5.2947</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6839</v>
+        <v>0.8557</v>
       </c>
       <c r="J37" t="n">
-        <v>18.4653</v>
+        <v>23.1039</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>0.79</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2985</v>
+        <v>-0.2227</v>
       </c>
       <c r="J38" t="n">
-        <v>-8.0595</v>
+        <v>-6.0129</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>0.62</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5737</v>
+        <v>-0.3822</v>
       </c>
       <c r="J39" t="n">
-        <v>-15.4899</v>
+        <v>-10.3194</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>0.61</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3915</v>
       </c>
       <c r="J40" t="n">
-        <v>-15.8544</v>
+        <v>-10.5705</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.49</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7418</v>
+        <v>-0.5031</v>
       </c>
       <c r="J41" t="n">
-        <v>-20.0286</v>
+        <v>-13.5837</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.19</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5768</v>
+        <v>0.5562</v>
       </c>
       <c r="J42" t="n">
-        <v>14.42</v>
+        <v>13.905</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4957</v>
+        <v>0.4798</v>
       </c>
       <c r="J43" t="n">
-        <v>12.3925</v>
+        <v>11.995</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.09</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2659</v>
+        <v>0.2948</v>
       </c>
       <c r="J44" t="n">
-        <v>6.6475</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>1.06</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1656</v>
+        <v>0.2067</v>
       </c>
       <c r="J45" t="n">
-        <v>4.14</v>
+        <v>5.1675</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>1.03</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0594</v>
+        <v>0.108</v>
       </c>
       <c r="J46" t="n">
-        <v>1.485</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.01</v>
       </c>
       <c r="I47" t="n">
-        <v>0.056</v>
+        <v>0.0423</v>
       </c>
       <c r="J47" t="n">
-        <v>1.4</v>
+        <v>1.0575</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.02</v>
+        <v>0.0039</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5</v>
+        <v>0.0975</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>0.97</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0746</v>
+        <v>-0.0479</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.865</v>
+        <v>-1.1975</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1433</v>
+        <v>-0.0854</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.5825</v>
+        <v>-2.135</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1433</v>
+        <v>-0.0854</v>
       </c>
       <c r="J51" t="n">
-        <v>-3.5825</v>
+        <v>-2.135</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.3</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5347</v>
+        <v>0.6343</v>
       </c>
       <c r="J52" t="n">
-        <v>16.041</v>
+        <v>19.029</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>0.96</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0861</v>
+        <v>-0.06</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.583</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.136</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.08</v>
+        <v>-2.523</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.87</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2644</v>
+        <v>-0.162</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.932</v>
+        <v>-4.86</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.72</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4855</v>
+        <v>-0.3123</v>
       </c>
       <c r="J56" t="n">
-        <v>-14.565</v>
+        <v>-9.369</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.45</v>
       </c>
       <c r="I57" t="n">
-        <v>1.1553</v>
+        <v>1.094</v>
       </c>
       <c r="J57" t="n">
-        <v>34.659</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.37</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9866</v>
+        <v>0.9717</v>
       </c>
       <c r="J58" t="n">
-        <v>29.598</v>
+        <v>29.151</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.99</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1546</v>
+        <v>-0.0861</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.638</v>
+        <v>-2.583</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.96</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2704</v>
+        <v>-0.1994</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.112</v>
+        <v>-5.982</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.89</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.482</v>
+        <v>-0.4147</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.46</v>
+        <v>-12.441</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.47</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7359</v>
+        <v>0.9135</v>
       </c>
       <c r="J62" t="n">
-        <v>21.3411</v>
+        <v>26.4915</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.06</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1637</v>
+        <v>0.1663</v>
       </c>
       <c r="J63" t="n">
-        <v>4.7473</v>
+        <v>4.8227</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.87</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2716</v>
+        <v>-0.1646</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.8764</v>
+        <v>-4.7734</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3642</v>
+        <v>-0.2266</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.5618</v>
+        <v>-6.5714</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5296</v>
+        <v>-0.3434</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.3584</v>
+        <v>-9.958600000000001</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.18</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.5271</v>
       </c>
       <c r="J67" t="n">
-        <v>15.6832</v>
+        <v>15.2859</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.17</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5135</v>
+        <v>0.5018</v>
       </c>
       <c r="J68" t="n">
-        <v>14.8915</v>
+        <v>14.5522</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.14</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4265</v>
+        <v>0.4251</v>
       </c>
       <c r="J69" t="n">
-        <v>12.3685</v>
+        <v>12.3279</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.07</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1894</v>
+        <v>0.2339</v>
       </c>
       <c r="J70" t="n">
-        <v>5.4926</v>
+        <v>6.7831</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>1.04</v>
       </c>
       <c r="I71" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.1391</v>
       </c>
       <c r="J71" t="n">
-        <v>2.552</v>
+        <v>4.0339</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.83</v>
       </c>
       <c r="I72" t="n">
-        <v>1.7132</v>
+        <v>1.4771</v>
       </c>
       <c r="J72" t="n">
-        <v>34.264</v>
+        <v>29.542</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.72</v>
       </c>
       <c r="I73" t="n">
-        <v>1.5164</v>
+        <v>1.3515</v>
       </c>
       <c r="J73" t="n">
-        <v>30.328</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.4</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8383</v>
+        <v>0.9559</v>
       </c>
       <c r="J74" t="n">
-        <v>16.766</v>
+        <v>19.118</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.26</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5302</v>
+        <v>0.6482</v>
       </c>
       <c r="J75" t="n">
-        <v>10.604</v>
+        <v>12.964</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.18</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3449</v>
+        <v>0.4537</v>
       </c>
       <c r="J76" t="n">
-        <v>6.898</v>
+        <v>9.074</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.07</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3339</v>
+        <v>0.3733</v>
       </c>
       <c r="J77" t="n">
-        <v>6.678</v>
+        <v>7.466</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>0.58</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.5748</v>
+        <v>-0.3963</v>
       </c>
       <c r="J78" t="n">
-        <v>-11.496</v>
+        <v>-7.926</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.58</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.5748</v>
+        <v>-0.3963</v>
       </c>
       <c r="J79" t="n">
-        <v>-11.496</v>
+        <v>-7.926</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.53</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6489</v>
+        <v>-0.4428</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.978</v>
+        <v>-8.856</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.4</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.8229</v>
+        <v>-0.5656</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.458</v>
+        <v>-11.312</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.35</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9946</v>
+        <v>0.969</v>
       </c>
       <c r="J82" t="n">
-        <v>28.8434</v>
+        <v>28.101</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.11</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4001</v>
+        <v>0.3648</v>
       </c>
       <c r="J83" t="n">
-        <v>11.6029</v>
+        <v>10.5792</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>0.97</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1876</v>
+        <v>-0.1394</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.4404</v>
+        <v>-4.0426</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.88</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4729</v>
+        <v>-0.4168</v>
       </c>
       <c r="J85" t="n">
-        <v>-13.7141</v>
+        <v>-12.0872</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.88</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4729</v>
+        <v>-0.4168</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.7141</v>
+        <v>-12.0872</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.33</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5483</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>15.9007</v>
+        <v>19.0472</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.29</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4965</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="J88" t="n">
-        <v>14.3985</v>
+        <v>17.0578</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>1.05</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1196</v>
+        <v>0.1337</v>
       </c>
       <c r="J89" t="n">
-        <v>3.4684</v>
+        <v>3.8773</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.84</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3323</v>
+        <v>-0.202</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.636699999999999</v>
+        <v>-5.858</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.65</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5891</v>
+        <v>-0.3865</v>
       </c>
       <c r="J91" t="n">
-        <v>-17.0839</v>
+        <v>-11.2085</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.646</v>
+        <v>0.7889</v>
       </c>
       <c r="J92" t="n">
-        <v>17.442</v>
+        <v>21.3003</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>0.95</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.0664</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.9305</v>
+        <v>-1.7928</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.82</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3231</v>
+        <v>-0.2064</v>
       </c>
       <c r="J94" t="n">
-        <v>-8.723699999999999</v>
+        <v>-5.5728</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.78</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3846</v>
+        <v>-0.2462</v>
       </c>
       <c r="J95" t="n">
-        <v>-10.3842</v>
+        <v>-6.6474</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6783</v>
+        <v>-0.4543</v>
       </c>
       <c r="J96" t="n">
-        <v>-18.3141</v>
+        <v>-12.2661</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.32</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8739</v>
+        <v>0.8605</v>
       </c>
       <c r="J97" t="n">
-        <v>23.5953</v>
+        <v>23.2335</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.27</v>
       </c>
       <c r="I98" t="n">
-        <v>0.758</v>
+        <v>0.7426</v>
       </c>
       <c r="J98" t="n">
-        <v>20.466</v>
+        <v>20.0502</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.09</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2426</v>
+        <v>0.2887</v>
       </c>
       <c r="J99" t="n">
-        <v>6.5502</v>
+        <v>7.7949</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.06</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1471</v>
+        <v>0.1997</v>
       </c>
       <c r="J100" t="n">
-        <v>3.9717</v>
+        <v>5.3919</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3374</v>
+        <v>-0.2661</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.1098</v>
+        <v>-7.1847</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.02</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2189</v>
+        <v>0.2132</v>
       </c>
       <c r="J102" t="n">
-        <v>4.378</v>
+        <v>4.264</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>0.87</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1054</v>
+        <v>-0.1114</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.108</v>
+        <v>-2.228</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.58</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.5885</v>
+        <v>-0.4011</v>
       </c>
       <c r="J104" t="n">
-        <v>-11.77</v>
+        <v>-8.022</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.43</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7917</v>
+        <v>-0.5419</v>
       </c>
       <c r="J105" t="n">
-        <v>-15.834</v>
+        <v>-10.838</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.4</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8294</v>
+        <v>-0.5702</v>
       </c>
       <c r="J106" t="n">
-        <v>-16.588</v>
+        <v>-11.404</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>2.25</v>
       </c>
       <c r="I107" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J107" t="n">
-        <v>41.186</v>
+        <v>36.676</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.45</v>
       </c>
       <c r="I108" t="n">
-        <v>0.9298</v>
+        <v>1.032</v>
       </c>
       <c r="J108" t="n">
-        <v>18.596</v>
+        <v>20.64</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.41</v>
       </c>
       <c r="I109" t="n">
-        <v>0.8439</v>
+        <v>0.9687</v>
       </c>
       <c r="J109" t="n">
-        <v>16.878</v>
+        <v>19.374</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.32</v>
       </c>
       <c r="I110" t="n">
-        <v>0.651</v>
+        <v>0.7785</v>
       </c>
       <c r="J110" t="n">
-        <v>13.02</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>1.14</v>
       </c>
       <c r="I111" t="n">
-        <v>0.2381</v>
+        <v>0.3428</v>
       </c>
       <c r="J111" t="n">
-        <v>4.762</v>
+        <v>6.856</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.04</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2354</v>
+        <v>0.2302</v>
       </c>
       <c r="J112" t="n">
-        <v>5.4142</v>
+        <v>5.2946</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>0.86</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1488</v>
+        <v>-0.1383</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.4224</v>
+        <v>-3.1809</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.57</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.6231</v>
+        <v>-0.4196</v>
       </c>
       <c r="J114" t="n">
-        <v>-14.3313</v>
+        <v>-9.6508</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.57</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6231</v>
+        <v>-0.4196</v>
       </c>
       <c r="J115" t="n">
-        <v>-14.3313</v>
+        <v>-9.6508</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.53</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6766</v>
+        <v>-0.457</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.5618</v>
+        <v>-10.511</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.64</v>
       </c>
       <c r="I117" t="n">
-        <v>1.3949</v>
+        <v>1.2692</v>
       </c>
       <c r="J117" t="n">
-        <v>32.0827</v>
+        <v>29.1916</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.6</v>
       </c>
       <c r="I118" t="n">
-        <v>1.3182</v>
+        <v>1.2218</v>
       </c>
       <c r="J118" t="n">
-        <v>30.3186</v>
+        <v>28.1014</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.51</v>
       </c>
       <c r="I119" t="n">
-        <v>1.1378</v>
+        <v>1.1143</v>
       </c>
       <c r="J119" t="n">
-        <v>26.1694</v>
+        <v>25.6289</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.34</v>
       </c>
       <c r="I120" t="n">
-        <v>0.735</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="J120" t="n">
-        <v>16.905</v>
+        <v>19.3706</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.98</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2829</v>
+        <v>-0.1937</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.5067</v>
+        <v>-4.4551</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>2.31</v>
       </c>
       <c r="I122" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J122" t="n">
-        <v>43.2453</v>
+        <v>38.5098</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.45</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9995000000000001</v>
+        <v>1.0396</v>
       </c>
       <c r="J123" t="n">
-        <v>20.9895</v>
+        <v>21.8316</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.4</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8671</v>
+        <v>0.9634</v>
       </c>
       <c r="J124" t="n">
-        <v>18.2091</v>
+        <v>20.2314</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.2</v>
       </c>
       <c r="I125" t="n">
-        <v>0.4079</v>
+        <v>0.5145</v>
       </c>
       <c r="J125" t="n">
-        <v>8.565899999999999</v>
+        <v>10.8045</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.77</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.8419</v>
+        <v>-0.7974</v>
       </c>
       <c r="J126" t="n">
-        <v>-17.6799</v>
+        <v>-16.7454</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.03</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1973</v>
+        <v>0.18</v>
       </c>
       <c r="J127" t="n">
-        <v>4.1433</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>0.98</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0564</v>
+        <v>0.0086</v>
       </c>
       <c r="J128" t="n">
-        <v>1.1844</v>
+        <v>0.1806</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.184</v>
+        <v>-0.1578</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.864</v>
+        <v>-3.3138</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.46</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.7744</v>
+        <v>-0.5278</v>
       </c>
       <c r="J130" t="n">
-        <v>-16.2624</v>
+        <v>-11.0838</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.44</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7988</v>
+        <v>-0.5463</v>
       </c>
       <c r="J131" t="n">
-        <v>-16.7748</v>
+        <v>-11.4723</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>2.04</v>
       </c>
       <c r="I132" t="n">
-        <v>2.0097</v>
+        <v>1.718</v>
       </c>
       <c r="J132" t="n">
-        <v>46.2231</v>
+        <v>39.514</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.65</v>
       </c>
       <c r="I133" t="n">
-        <v>1.3954</v>
+        <v>1.274</v>
       </c>
       <c r="J133" t="n">
-        <v>32.0942</v>
+        <v>29.302</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.58</v>
       </c>
       <c r="I134" t="n">
-        <v>1.2594</v>
+        <v>1.192</v>
       </c>
       <c r="J134" t="n">
-        <v>28.9662</v>
+        <v>27.416</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>1.21</v>
       </c>
       <c r="I135" t="n">
-        <v>0.4222</v>
+        <v>0.5329</v>
       </c>
       <c r="J135" t="n">
-        <v>9.710599999999999</v>
+        <v>12.2567</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.8</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.779</v>
+        <v>-0.7272</v>
       </c>
       <c r="J136" t="n">
-        <v>-17.917</v>
+        <v>-16.7256</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>0.85</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1414</v>
+        <v>-0.1365</v>
       </c>
       <c r="J137" t="n">
-        <v>-3.2522</v>
+        <v>-3.1395</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>0.78</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2533</v>
+        <v>-0.2132</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.8259</v>
+        <v>-4.9036</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.66</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4619</v>
+        <v>-0.329</v>
       </c>
       <c r="J139" t="n">
-        <v>-10.6237</v>
+        <v>-7.567</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.66</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4619</v>
+        <v>-0.329</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.6237</v>
+        <v>-7.567</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.38</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.8555</v>
+        <v>-0.5899</v>
       </c>
       <c r="J141" t="n">
-        <v>-19.6765</v>
+        <v>-13.5677</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>1.3786</v>
+        <v>1.2412</v>
       </c>
       <c r="J142" t="n">
-        <v>41.358</v>
+        <v>37.236</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.28</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7667</v>
+        <v>0.758</v>
       </c>
       <c r="J143" t="n">
-        <v>23.001</v>
+        <v>22.74</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.26</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7187</v>
+        <v>0.7108</v>
       </c>
       <c r="J144" t="n">
-        <v>21.561</v>
+        <v>21.324</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.88</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5189</v>
+        <v>-0.4509</v>
       </c>
       <c r="J145" t="n">
-        <v>-15.567</v>
+        <v>-13.527</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.82</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.672</v>
+        <v>-0.6137</v>
       </c>
       <c r="J146" t="n">
-        <v>-20.16</v>
+        <v>-18.411</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.36</v>
       </c>
       <c r="I147" t="n">
-        <v>0.621</v>
+        <v>0.7528</v>
       </c>
       <c r="J147" t="n">
-        <v>18.63</v>
+        <v>22.584</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.1</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2545</v>
+        <v>0.2667</v>
       </c>
       <c r="J148" t="n">
-        <v>7.635</v>
+        <v>8.000999999999999</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>1.01</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0751</v>
+        <v>0.0518</v>
       </c>
       <c r="J149" t="n">
-        <v>2.253</v>
+        <v>1.554</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.64</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5846</v>
+        <v>-0.3845</v>
       </c>
       <c r="J150" t="n">
-        <v>-17.538</v>
+        <v>-11.535</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.54</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7079</v>
+        <v>-0.4764</v>
       </c>
       <c r="J151" t="n">
-        <v>-21.237</v>
+        <v>-14.292</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.58</v>
       </c>
       <c r="I152" t="n">
-        <v>1.3123</v>
+        <v>1.2105</v>
       </c>
       <c r="J152" t="n">
-        <v>31.4952</v>
+        <v>29.052</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.53</v>
       </c>
       <c r="I153" t="n">
-        <v>1.2138</v>
+        <v>1.1495</v>
       </c>
       <c r="J153" t="n">
-        <v>29.1312</v>
+        <v>27.588</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>1.32</v>
       </c>
       <c r="I154" t="n">
-        <v>0.7298</v>
+        <v>0.8109</v>
       </c>
       <c r="J154" t="n">
-        <v>17.5152</v>
+        <v>19.4616</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>1.19</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4133</v>
+        <v>0.5077</v>
       </c>
       <c r="J155" t="n">
-        <v>9.9192</v>
+        <v>12.1848</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>1.09</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1528</v>
+        <v>0.2408</v>
       </c>
       <c r="J156" t="n">
-        <v>3.6672</v>
+        <v>5.7792</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>0.89</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.1116</v>
+        <v>-0.1107</v>
       </c>
       <c r="J157" t="n">
-        <v>-2.6784</v>
+        <v>-2.6568</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>0.88</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1287</v>
+        <v>-0.1223</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.0888</v>
+        <v>-2.9352</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>0.83</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2121</v>
+        <v>-0.1772</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.0904</v>
+        <v>-4.2528</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.64</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.535</v>
+        <v>-0.3585</v>
       </c>
       <c r="J160" t="n">
-        <v>-12.84</v>
+        <v>-8.603999999999999</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.47</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.76</v>
+        <v>-0.5171</v>
       </c>
       <c r="J161" t="n">
-        <v>-18.24</v>
+        <v>-12.4104</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.93</v>
       </c>
       <c r="I162" t="n">
-        <v>1.8839</v>
+        <v>1.5921</v>
       </c>
       <c r="J162" t="n">
-        <v>37.678</v>
+        <v>31.842</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.66</v>
       </c>
       <c r="I163" t="n">
-        <v>1.409</v>
+        <v>1.2838</v>
       </c>
       <c r="J163" t="n">
-        <v>28.18</v>
+        <v>25.676</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.5</v>
       </c>
       <c r="I164" t="n">
-        <v>1.0857</v>
+        <v>1.0964</v>
       </c>
       <c r="J164" t="n">
-        <v>21.714</v>
+        <v>21.928</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>1.34</v>
       </c>
       <c r="I165" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.832</v>
       </c>
       <c r="J165" t="n">
-        <v>14.224</v>
+        <v>16.64</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.91</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5103</v>
+        <v>-0.4324</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.206</v>
+        <v>-8.648</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1515</v>
+        <v>0.1274</v>
       </c>
       <c r="J167" t="n">
-        <v>3.03</v>
+        <v>2.548</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>0.77</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2745</v>
+        <v>-0.2259</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.49</v>
+        <v>-4.518</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>0.65</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.488</v>
+        <v>-0.3392</v>
       </c>
       <c r="J169" t="n">
-        <v>-9.76</v>
+        <v>-6.784</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.61</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5513</v>
+        <v>-0.376</v>
       </c>
       <c r="J170" t="n">
-        <v>-11.026</v>
+        <v>-7.52</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.35</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.8938</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="J171" t="n">
-        <v>-17.876</v>
+        <v>-12.39</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4328/event_4328_evp_summary.xlsx
+++ b/database/event/4328/event_4328_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.9371</v>
+        <v>4.6165</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1245</v>
+        <v>1.0514</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5908</v>
+        <v>1.4773</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9371</v>
+        <v>4.6165</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9085</v>
+        <v>2.592</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0286</v>
+        <v>2.0245</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0268</v>
+        <v>2.9481</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0268</v>
+        <v>2.9481</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0286</v>
+        <v>2.0245</v>
       </c>
       <c r="K2" t="n">
         <v>127</v>
@@ -529,7 +529,7 @@
         <v>54</v>
       </c>
       <c r="M2" t="n">
-        <v>5.055400000000001</v>
+        <v>4.9726</v>
       </c>
       <c r="N2" t="n">
         <v>181</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.4415</v>
+        <v>3.1215</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.7109</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9157</v>
+        <v>0.7968</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4415</v>
+        <v>3.1215</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9135</v>
+        <v>2.5981</v>
       </c>
       <c r="G3" t="n">
-        <v>0.528</v>
+        <v>0.5234</v>
       </c>
       <c r="H3" t="n">
-        <v>3.0378</v>
+        <v>2.9616</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0378</v>
+        <v>2.9616</v>
       </c>
       <c r="J3" t="n">
-        <v>0.528</v>
+        <v>0.5234</v>
       </c>
       <c r="K3" t="n">
         <v>132</v>
@@ -575,7 +575,7 @@
         <v>54</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5658</v>
+        <v>3.485</v>
       </c>
       <c r="N3" t="n">
         <v>186</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.4006</v>
+        <v>3.0545</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7745</v>
+        <v>0.6957</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8972</v>
+        <v>0.7663</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4006</v>
+        <v>3.0545</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8489</v>
+        <v>2.5504</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5517</v>
+        <v>0.5041</v>
       </c>
       <c r="H4" t="n">
-        <v>2.896</v>
+        <v>2.8571</v>
       </c>
       <c r="I4" t="n">
-        <v>2.896</v>
+        <v>2.8571</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5517</v>
+        <v>0.5041</v>
       </c>
       <c r="K4" t="n">
         <v>132</v>
@@ -621,7 +621,7 @@
         <v>54</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4477</v>
+        <v>3.3612</v>
       </c>
       <c r="N4" t="n">
         <v>186</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.238</v>
+        <v>2.8727</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7375</v>
+        <v>0.6543</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8238</v>
+        <v>0.6835</v>
       </c>
       <c r="E5" t="n">
-        <v>3.238</v>
+        <v>2.8727</v>
       </c>
       <c r="F5" t="n">
-        <v>3.238</v>
+        <v>2.8727</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7503</v>
+        <v>3.5625</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7503</v>
+        <v>3.5625</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7503</v>
+        <v>3.5625</v>
       </c>
       <c r="N5" t="n">
         <v>137</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.8633</v>
+        <v>2.5275</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6521</v>
+        <v>0.5757</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6546</v>
+        <v>0.5264</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8633</v>
+        <v>2.5275</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5023</v>
+        <v>3.1949</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.639</v>
+        <v>-0.6674</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3307</v>
+        <v>4.2676</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3307</v>
+        <v>4.2676</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.639</v>
+        <v>-0.6674</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -713,7 +713,7 @@
         <v>54</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6917</v>
+        <v>3.6002</v>
       </c>
       <c r="N6" t="n">
         <v>186</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8475</v>
+        <v>2.5096</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6485</v>
+        <v>0.5716</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6475</v>
+        <v>0.5182</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8475</v>
+        <v>2.5096</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8475</v>
+        <v>2.5096</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8928</v>
+        <v>2.7679</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8928</v>
+        <v>2.7679</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8928</v>
+        <v>2.7679</v>
       </c>
       <c r="N7" t="n">
         <v>117</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4389</v>
+        <v>2.309</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5555</v>
+        <v>0.5259</v>
       </c>
       <c r="D8" t="n">
-        <v>0.463</v>
+        <v>0.4269</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4389</v>
+        <v>2.309</v>
       </c>
       <c r="F8" t="n">
-        <v>1.851</v>
+        <v>1.7576</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5879</v>
+        <v>0.5514</v>
       </c>
       <c r="H8" t="n">
-        <v>1.851</v>
+        <v>1.7576</v>
       </c>
       <c r="I8" t="n">
-        <v>1.851</v>
+        <v>1.7576</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5879</v>
+        <v>0.5514</v>
       </c>
       <c r="K8" t="n">
         <v>127</v>
@@ -805,7 +805,7 @@
         <v>54</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4389</v>
+        <v>2.309</v>
       </c>
       <c r="N8" t="n">
         <v>181</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.346</v>
+        <v>2.2539</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5343</v>
+        <v>0.5133</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4211</v>
+        <v>0.4018</v>
       </c>
       <c r="E9" t="n">
-        <v>2.346</v>
+        <v>2.2539</v>
       </c>
       <c r="F9" t="n">
-        <v>2.346</v>
+        <v>2.2539</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.346</v>
+        <v>2.2539</v>
       </c>
       <c r="I9" t="n">
-        <v>2.346</v>
+        <v>2.2539</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.346</v>
+        <v>2.2539</v>
       </c>
       <c r="N9" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3026</v>
+        <v>2.1672</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5244</v>
+        <v>0.4936</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4015</v>
+        <v>0.3624</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3026</v>
+        <v>2.1672</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3026</v>
+        <v>2.1672</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3026</v>
+        <v>2.1672</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3026</v>
+        <v>2.1672</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3026</v>
+        <v>2.1672</v>
       </c>
       <c r="N10" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.0962</v>
+        <v>1.9816</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4774</v>
+        <v>0.4513</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3083</v>
+        <v>0.2779</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0962</v>
+        <v>1.9816</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5737</v>
+        <v>2.4084</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4775</v>
+        <v>-0.4268</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5737</v>
+        <v>2.5463</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5737</v>
+        <v>2.5463</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4775</v>
+        <v>-0.4268</v>
       </c>
       <c r="K11" t="n">
         <v>127</v>
@@ -943,7 +943,7 @@
         <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0962</v>
+        <v>2.1195</v>
       </c>
       <c r="N11" t="n">
         <v>181</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5996</v>
+        <v>1.7904</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3643</v>
+        <v>0.4078</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.1908</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5996</v>
+        <v>1.7904</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5996</v>
+        <v>1.7904</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5996</v>
+        <v>1.7904</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5996</v>
+        <v>1.7904</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5996</v>
+        <v>1.7904</v>
       </c>
       <c r="N12" t="n">
         <v>120</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>roman</t>
+          <t>xseveN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.5586</v>
+        <v>1.4728</v>
       </c>
       <c r="C13" t="n">
-        <v>0.355</v>
+        <v>0.3354</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0462</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5586</v>
+        <v>1.4728</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5586</v>
+        <v>0.5523</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.9205</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5586</v>
+        <v>0.5523</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5586</v>
+        <v>0.5523</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.9205</v>
       </c>
       <c r="K13" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5586</v>
+        <v>1.4728</v>
       </c>
       <c r="N13" t="n">
-        <v>123</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>xseveN</t>
+          <t>roman</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4833</v>
+        <v>1.426</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3378</v>
+        <v>0.3248</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0316</v>
+        <v>0.0249</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4833</v>
+        <v>1.426</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5337</v>
+        <v>1.426</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9496</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5337</v>
+        <v>1.426</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5337</v>
+        <v>1.426</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9496</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L14" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4833</v>
+        <v>1.426</v>
       </c>
       <c r="N14" t="n">
-        <v>181</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.325</v>
+        <v>1.2443</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3018</v>
+        <v>0.2834</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0398</v>
+        <v>-0.0578</v>
       </c>
       <c r="E15" t="n">
-        <v>1.325</v>
+        <v>1.2443</v>
       </c>
       <c r="F15" t="n">
-        <v>1.325</v>
+        <v>1.2443</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.325</v>
+        <v>1.2443</v>
       </c>
       <c r="I15" t="n">
-        <v>1.325</v>
+        <v>1.2443</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.325</v>
+        <v>1.2443</v>
       </c>
       <c r="N15" t="n">
         <v>120</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2312</v>
+        <v>1.2198</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2804</v>
+        <v>0.2778</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0822</v>
+        <v>-0.0689</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2312</v>
+        <v>1.2198</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2312</v>
+        <v>1.2198</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2312</v>
+        <v>1.2198</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2312</v>
+        <v>1.2198</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2312</v>
+        <v>1.2198</v>
       </c>
       <c r="N16" t="n">
         <v>117</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.133</v>
+        <v>1.11</v>
       </c>
       <c r="C17" t="n">
-        <v>0.258</v>
+        <v>0.2528</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1265</v>
+        <v>-0.1189</v>
       </c>
       <c r="E17" t="n">
-        <v>1.133</v>
+        <v>1.11</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.8858</v>
       </c>
       <c r="G17" t="n">
-        <v>0.194</v>
+        <v>0.2242</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.8858</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.8858</v>
       </c>
       <c r="J17" t="n">
-        <v>0.194</v>
+        <v>0.2242</v>
       </c>
       <c r="K17" t="n">
         <v>127</v>
@@ -1219,7 +1219,7 @@
         <v>54</v>
       </c>
       <c r="M17" t="n">
-        <v>1.133</v>
+        <v>1.11</v>
       </c>
       <c r="N17" t="n">
         <v>181</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0883</v>
+        <v>1.0183</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2479</v>
+        <v>0.2319</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1467</v>
+        <v>-0.1607</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0883</v>
+        <v>1.0183</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8308</v>
+        <v>1.0183</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7425</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8308</v>
+        <v>1.0183</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8308</v>
+        <v>1.0183</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7425</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="L18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0883</v>
+        <v>1.0183</v>
       </c>
       <c r="N18" t="n">
-        <v>186</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.067</v>
+        <v>1.0033</v>
       </c>
       <c r="C19" t="n">
-        <v>0.243</v>
+        <v>0.2285</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1563</v>
+        <v>-0.1675</v>
       </c>
       <c r="E19" t="n">
-        <v>1.067</v>
+        <v>1.0033</v>
       </c>
       <c r="F19" t="n">
-        <v>1.067</v>
+        <v>1.7704</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.7671</v>
       </c>
       <c r="H19" t="n">
-        <v>1.067</v>
+        <v>1.7704</v>
       </c>
       <c r="I19" t="n">
-        <v>1.067</v>
+        <v>1.7704</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.7671</v>
       </c>
       <c r="K19" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M19" t="n">
-        <v>1.067</v>
+        <v>1.0033</v>
       </c>
       <c r="N19" t="n">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.827</v>
+        <v>0.7331</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1884</v>
+        <v>0.167</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2647</v>
+        <v>-0.2905</v>
       </c>
       <c r="E20" t="n">
-        <v>0.827</v>
+        <v>0.7331</v>
       </c>
       <c r="F20" t="n">
-        <v>0.827</v>
+        <v>0.7331</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.827</v>
+        <v>0.7331</v>
       </c>
       <c r="I20" t="n">
-        <v>0.827</v>
+        <v>0.7331</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.827</v>
+        <v>0.7331</v>
       </c>
       <c r="N20" t="n">
         <v>117</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.496</v>
+        <v>0.6575</v>
       </c>
       <c r="C21" t="n">
-        <v>0.113</v>
+        <v>0.1497</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4141</v>
+        <v>-0.3249</v>
       </c>
       <c r="E21" t="n">
-        <v>0.496</v>
+        <v>0.6575</v>
       </c>
       <c r="F21" t="n">
-        <v>0.496</v>
+        <v>0.6575</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.496</v>
+        <v>0.6575</v>
       </c>
       <c r="I21" t="n">
-        <v>0.496</v>
+        <v>0.6575</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.496</v>
+        <v>0.6575</v>
       </c>
       <c r="N21" t="n">
         <v>123</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2682</v>
+        <v>0.1707</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0611</v>
+        <v>0.0389</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5169</v>
+        <v>-0.5465</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2682</v>
+        <v>0.1707</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2682</v>
+        <v>0.1707</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2682</v>
+        <v>0.1707</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2682</v>
+        <v>0.1707</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2682</v>
+        <v>0.1707</v>
       </c>
       <c r="N22" t="n">
         <v>123</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1264</v>
+        <v>0.1127</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0288</v>
+        <v>0.0257</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.581</v>
+        <v>-0.5729</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1264</v>
+        <v>0.1127</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1264</v>
+        <v>0.1127</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1264</v>
+        <v>0.1127</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1264</v>
+        <v>0.1127</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1264</v>
+        <v>0.1127</v>
       </c>
       <c r="N23" t="n">
         <v>123</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0736</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0168</v>
+        <v>0.0152</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6048</v>
+        <v>-0.5939</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0736</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1363</v>
+        <v>0.1417</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.0751</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1363</v>
+        <v>0.1417</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1363</v>
+        <v>0.1417</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.0751</v>
       </c>
       <c r="K24" t="n">
         <v>132</v>
@@ -1541,7 +1541,7 @@
         <v>54</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0736</v>
+        <v>0.06659999999999999</v>
       </c>
       <c r="N24" t="n">
         <v>186</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.0584</v>
+        <v>-0.1633</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0133</v>
+        <v>-0.0372</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6644</v>
+        <v>-0.6985</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0584</v>
+        <v>-0.1633</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0584</v>
+        <v>-0.1633</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0584</v>
+        <v>-0.1633</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0584</v>
+        <v>-0.1633</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0584</v>
+        <v>-0.1633</v>
       </c>
       <c r="N25" t="n">
         <v>137</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1391</v>
+        <v>-0.177</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0317</v>
+        <v>-0.0403</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7008</v>
+        <v>-0.7048</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1391</v>
+        <v>-0.177</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1391</v>
+        <v>-0.177</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1391</v>
+        <v>-0.177</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1391</v>
+        <v>-0.177</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1391</v>
+        <v>-0.177</v>
       </c>
       <c r="N26" t="n">
         <v>120</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2169</v>
+        <v>-0.3048</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0494</v>
+        <v>-0.0694</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7359</v>
+        <v>-0.763</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2169</v>
+        <v>-0.3048</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2169</v>
+        <v>-0.3048</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2169</v>
+        <v>-0.3048</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2169</v>
+        <v>-0.3048</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2169</v>
+        <v>-0.3048</v>
       </c>
       <c r="N27" t="n">
         <v>137</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.5132</v>
+        <v>-0.5726</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1169</v>
+        <v>-0.1304</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8697</v>
+        <v>-0.8849</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5132</v>
+        <v>-0.5726</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.5132</v>
+        <v>-0.5726</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.5132</v>
+        <v>-0.5726</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5132</v>
+        <v>-0.5726</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.5132</v>
+        <v>-0.5726</v>
       </c>
       <c r="N28" t="n">
         <v>123</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.3849</v>
+        <v>-1.333</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3154</v>
+        <v>-0.3036</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.2632</v>
+        <v>-1.231</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.3849</v>
+        <v>-1.333</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.3849</v>
+        <v>-1.333</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.3849</v>
+        <v>-1.333</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.3849</v>
+        <v>-1.333</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.3849</v>
+        <v>-1.333</v>
       </c>
       <c r="N29" t="n">
         <v>120</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.5432</v>
+        <v>-1.5755</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3515</v>
+        <v>-0.3588</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.3347</v>
+        <v>-1.3414</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.5432</v>
+        <v>-1.5755</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.5432</v>
+        <v>-1.5755</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.5432</v>
+        <v>-1.5755</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.5432</v>
+        <v>-1.5755</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.5432</v>
+        <v>-1.5755</v>
       </c>
       <c r="N30" t="n">
         <v>137</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.303</v>
+        <v>-2.3064</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.5245</v>
+        <v>-0.5253</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.6777</v>
+        <v>-1.6741</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.303</v>
+        <v>-2.3064</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.303</v>
+        <v>-2.3064</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.303</v>
+        <v>-2.3064</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.303</v>
+        <v>-2.3064</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.303</v>
+        <v>-2.3064</v>
       </c>
       <c r="N31" t="n">
         <v>137</v>
@@ -1969,10 +1969,10 @@
         <v>1.06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2106</v>
+        <v>0.2057</v>
       </c>
       <c r="J2" t="n">
-        <v>5.265</v>
+        <v>5.1425</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>0.91</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.107</v>
+        <v>-0.1232</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.675</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.87</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1508</v>
+        <v>-0.1679</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.77</v>
+        <v>-4.1975</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.7</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3167</v>
+        <v>-0.3324</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.9175</v>
+        <v>-8.31</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.68</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3357</v>
+        <v>-0.3507</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.3925</v>
+        <v>-8.7675</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.59</v>
       </c>
       <c r="I7" t="n">
-        <v>1.244</v>
+        <v>1.2906</v>
       </c>
       <c r="J7" t="n">
-        <v>31.1</v>
+        <v>32.265</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.29</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7599</v>
+        <v>0.7254</v>
       </c>
       <c r="J8" t="n">
-        <v>18.9975</v>
+        <v>18.135</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>1.29</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7599</v>
+        <v>0.7254</v>
       </c>
       <c r="J9" t="n">
-        <v>18.9975</v>
+        <v>18.135</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>1.03</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0736</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>1.84</v>
+        <v>2.415</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>1.02</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0365</v>
+        <v>0.0601</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9125</v>
+        <v>1.5025</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.34</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7025</v>
+        <v>0.672</v>
       </c>
       <c r="J12" t="n">
-        <v>20.3725</v>
+        <v>19.488</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3174</v>
+        <v>0.3177</v>
       </c>
       <c r="J13" t="n">
-        <v>9.204599999999999</v>
+        <v>9.2133</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0443</v>
+        <v>0.0481</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2847</v>
+        <v>1.3949</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.71</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3223</v>
+        <v>-0.335</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.3467</v>
+        <v>-9.715</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.62</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4068</v>
+        <v>-0.4164</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.7972</v>
+        <v>-12.0756</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.27</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7846</v>
+        <v>0.7339</v>
       </c>
       <c r="J17" t="n">
-        <v>22.7534</v>
+        <v>21.2831</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1897</v>
+        <v>0.1951</v>
       </c>
       <c r="J18" t="n">
-        <v>5.5013</v>
+        <v>5.6579</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1575</v>
+        <v>0.1641</v>
       </c>
       <c r="J19" t="n">
-        <v>4.5675</v>
+        <v>4.7589</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.172</v>
+        <v>-0.174</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.988</v>
+        <v>-5.046</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5511</v>
+        <v>-0.5234</v>
       </c>
       <c r="J21" t="n">
-        <v>-15.9819</v>
+        <v>-15.1786</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.28</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7624</v>
+        <v>0.7227</v>
       </c>
       <c r="J22" t="n">
-        <v>22.872</v>
+        <v>21.681</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.24</v>
       </c>
       <c r="I23" t="n">
-        <v>0.667</v>
+        <v>0.6385</v>
       </c>
       <c r="J23" t="n">
-        <v>20.01</v>
+        <v>19.155</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.22</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6187</v>
+        <v>0.5955</v>
       </c>
       <c r="J24" t="n">
-        <v>18.561</v>
+        <v>17.865</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.13</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3953</v>
+        <v>0.393</v>
       </c>
       <c r="J25" t="n">
-        <v>11.859</v>
+        <v>11.79</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4752</v>
+        <v>-0.4484</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.256</v>
+        <v>-13.452</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.06</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1729</v>
+        <v>0.1782</v>
       </c>
       <c r="J27" t="n">
-        <v>5.187</v>
+        <v>5.346</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.15</v>
+        <v>0.1556</v>
       </c>
       <c r="J28" t="n">
-        <v>4.5</v>
+        <v>4.668</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.017</v>
+        <v>-0.0226</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.51</v>
+        <v>-0.678</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.92</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1069</v>
+        <v>-0.12</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.207</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2828</v>
+        <v>-0.2967</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.484</v>
+        <v>-8.901</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.49</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1083</v>
+        <v>1.0724</v>
       </c>
       <c r="J32" t="n">
-        <v>29.9241</v>
+        <v>28.9548</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8386</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>22.6422</v>
+        <v>21.5163</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1.28</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7298</v>
+        <v>0.7004</v>
       </c>
       <c r="J34" t="n">
-        <v>19.7046</v>
+        <v>18.9108</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>1.28</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7298</v>
+        <v>0.7004</v>
       </c>
       <c r="J35" t="n">
-        <v>19.7046</v>
+        <v>18.9108</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>1.1</v>
       </c>
       <c r="I36" t="n">
-        <v>0.28</v>
+        <v>0.2946</v>
       </c>
       <c r="J36" t="n">
-        <v>7.56</v>
+        <v>7.9542</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8557</v>
+        <v>0.7912</v>
       </c>
       <c r="J37" t="n">
-        <v>23.1039</v>
+        <v>21.3624</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>0.79</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2227</v>
+        <v>-0.242</v>
       </c>
       <c r="J38" t="n">
-        <v>-6.0129</v>
+        <v>-6.534</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>0.62</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3822</v>
+        <v>-0.3971</v>
       </c>
       <c r="J39" t="n">
-        <v>-10.3194</v>
+        <v>-10.7217</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>0.61</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3915</v>
+        <v>-0.406</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.5705</v>
+        <v>-10.962</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.49</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5031</v>
+        <v>-0.5115</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.5837</v>
+        <v>-13.8105</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.19</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5562</v>
+        <v>0.5372</v>
       </c>
       <c r="J42" t="n">
-        <v>13.905</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4798</v>
+        <v>0.4684</v>
       </c>
       <c r="J43" t="n">
-        <v>11.995</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.09</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2948</v>
+        <v>0.2981</v>
       </c>
       <c r="J44" t="n">
-        <v>7.37</v>
+        <v>7.4525</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>1.06</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2067</v>
+        <v>0.2152</v>
       </c>
       <c r="J45" t="n">
-        <v>5.1675</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>1.03</v>
       </c>
       <c r="I46" t="n">
-        <v>0.108</v>
+        <v>0.1205</v>
       </c>
       <c r="J46" t="n">
-        <v>2.7</v>
+        <v>3.0125</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.01</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0423</v>
+        <v>0.0466</v>
       </c>
       <c r="J47" t="n">
-        <v>1.0575</v>
+        <v>1.165</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0039</v>
+        <v>0.0027</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0975</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>0.97</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0479</v>
+        <v>-0.0566</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.1975</v>
+        <v>-1.415</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0854</v>
+        <v>-0.0969</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.135</v>
+        <v>-2.4225</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0854</v>
+        <v>-0.0969</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.135</v>
+        <v>-2.4225</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.3</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6343</v>
+        <v>0.61</v>
       </c>
       <c r="J52" t="n">
-        <v>19.029</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>0.96</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.06</v>
+        <v>-0.0701</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.8</v>
+        <v>-2.103</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.0959</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.523</v>
+        <v>-2.877</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.87</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.162</v>
+        <v>-0.1765</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.86</v>
+        <v>-5.295</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.72</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3123</v>
+        <v>-0.3253</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.369</v>
+        <v>-9.759</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.45</v>
       </c>
       <c r="I57" t="n">
-        <v>1.094</v>
+        <v>1.0488</v>
       </c>
       <c r="J57" t="n">
-        <v>32.82</v>
+        <v>31.464</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.37</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9717</v>
+        <v>0.9095</v>
       </c>
       <c r="J58" t="n">
-        <v>29.151</v>
+        <v>27.285</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.99</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0861</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.583</v>
+        <v>-2.436</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.96</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1994</v>
+        <v>-0.193</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.982</v>
+        <v>-5.79</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.89</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4147</v>
+        <v>-0.3942</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.441</v>
+        <v>-11.826</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.47</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9135</v>
+        <v>0.8623</v>
       </c>
       <c r="J62" t="n">
-        <v>26.4915</v>
+        <v>25.0067</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.06</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1663</v>
+        <v>0.1734</v>
       </c>
       <c r="J63" t="n">
-        <v>4.8227</v>
+        <v>5.0286</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.87</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1646</v>
+        <v>-0.1784</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.7734</v>
+        <v>-5.1736</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2266</v>
+        <v>-0.2406</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.5714</v>
+        <v>-6.9774</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3434</v>
+        <v>-0.3551</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.958600000000001</v>
+        <v>-10.2979</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.18</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5271</v>
+        <v>0.5119</v>
       </c>
       <c r="J67" t="n">
-        <v>15.2859</v>
+        <v>14.8451</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.17</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5018</v>
+        <v>0.4891</v>
       </c>
       <c r="J68" t="n">
-        <v>14.5522</v>
+        <v>14.1839</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.14</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4251</v>
+        <v>0.4194</v>
       </c>
       <c r="J69" t="n">
-        <v>12.3279</v>
+        <v>12.1626</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.07</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2339</v>
+        <v>0.2418</v>
       </c>
       <c r="J70" t="n">
-        <v>6.7831</v>
+        <v>7.0122</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>1.04</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1391</v>
+        <v>0.1516</v>
       </c>
       <c r="J71" t="n">
-        <v>4.0339</v>
+        <v>4.3964</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.83</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4771</v>
+        <v>1.4722</v>
       </c>
       <c r="J72" t="n">
-        <v>29.542</v>
+        <v>29.444</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.72</v>
       </c>
       <c r="I73" t="n">
-        <v>1.3515</v>
+        <v>1.3392</v>
       </c>
       <c r="J73" t="n">
-        <v>27.03</v>
+        <v>26.784</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.4</v>
       </c>
       <c r="I74" t="n">
-        <v>0.9559</v>
+        <v>0.9087</v>
       </c>
       <c r="J74" t="n">
-        <v>19.118</v>
+        <v>18.174</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.26</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6482</v>
+        <v>0.635</v>
       </c>
       <c r="J75" t="n">
-        <v>12.964</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.18</v>
       </c>
       <c r="I76" t="n">
-        <v>0.4537</v>
+        <v>0.4612</v>
       </c>
       <c r="J76" t="n">
-        <v>9.074</v>
+        <v>9.224</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.07</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3733</v>
+        <v>0.3316</v>
       </c>
       <c r="J77" t="n">
-        <v>7.466</v>
+        <v>6.632</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>0.58</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.3963</v>
+        <v>-0.4145</v>
       </c>
       <c r="J78" t="n">
-        <v>-7.926</v>
+        <v>-8.289999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.58</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3963</v>
+        <v>-0.4145</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.926</v>
+        <v>-8.289999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.53</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4428</v>
+        <v>-0.4584</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.856</v>
+        <v>-9.167999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.4</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5656</v>
+        <v>-0.5727</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.312</v>
+        <v>-11.454</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.35</v>
       </c>
       <c r="I82" t="n">
-        <v>0.969</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>28.101</v>
+        <v>26.0913</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.11</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3648</v>
+        <v>0.3595</v>
       </c>
       <c r="J83" t="n">
-        <v>10.5792</v>
+        <v>10.4255</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>0.97</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1394</v>
+        <v>-0.1419</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.0426</v>
+        <v>-4.1151</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.88</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4168</v>
+        <v>-0.4017</v>
       </c>
       <c r="J85" t="n">
-        <v>-12.0872</v>
+        <v>-11.6493</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.88</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4168</v>
+        <v>-0.4017</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.0872</v>
+        <v>-11.6493</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.33</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6354</v>
       </c>
       <c r="J87" t="n">
-        <v>19.0472</v>
+        <v>18.4266</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.29</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="J88" t="n">
-        <v>17.0578</v>
+        <v>16.6199</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>1.05</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1337</v>
+        <v>0.1439</v>
       </c>
       <c r="J89" t="n">
-        <v>3.8773</v>
+        <v>4.1731</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.84</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.202</v>
+        <v>-0.2148</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.858</v>
+        <v>-6.2292</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.65</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3865</v>
+        <v>-0.3957</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.2085</v>
+        <v>-11.4753</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7889</v>
+        <v>0.7441</v>
       </c>
       <c r="J92" t="n">
-        <v>21.3003</v>
+        <v>20.0907</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>0.95</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0664</v>
+        <v>-0.0789</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.7928</v>
+        <v>-2.1303</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.82</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2064</v>
+        <v>-0.2227</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.5728</v>
+        <v>-6.0129</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.78</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2462</v>
+        <v>-0.2621</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.6474</v>
+        <v>-7.0767</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4543</v>
+        <v>-0.463</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.2661</v>
+        <v>-12.501</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.32</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8605</v>
+        <v>0.8079</v>
       </c>
       <c r="J97" t="n">
-        <v>23.2335</v>
+        <v>21.8133</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.27</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7426</v>
+        <v>0.7045</v>
       </c>
       <c r="J98" t="n">
-        <v>20.0502</v>
+        <v>19.0215</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.09</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2887</v>
+        <v>0.294</v>
       </c>
       <c r="J99" t="n">
-        <v>7.7949</v>
+        <v>7.938</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.06</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1997</v>
+        <v>0.2104</v>
       </c>
       <c r="J100" t="n">
-        <v>5.3919</v>
+        <v>5.6808</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2661</v>
+        <v>-0.2562</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.1847</v>
+        <v>-6.9174</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.02</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2132</v>
+        <v>0.1814</v>
       </c>
       <c r="J102" t="n">
-        <v>4.264</v>
+        <v>3.628</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>0.87</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1114</v>
+        <v>-0.1372</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.228</v>
+        <v>-2.744</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.58</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.4011</v>
+        <v>-0.4183</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.022</v>
+        <v>-8.366</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.43</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5419</v>
+        <v>-0.5501</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.838</v>
+        <v>-11.002</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.4</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5702</v>
+        <v>-0.5763</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.404</v>
+        <v>-11.526</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>2.25</v>
       </c>
       <c r="I107" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J107" t="n">
-        <v>36.676</v>
+        <v>38.744</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.45</v>
       </c>
       <c r="I108" t="n">
-        <v>1.032</v>
+        <v>0.9901</v>
       </c>
       <c r="J108" t="n">
-        <v>20.64</v>
+        <v>19.802</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.41</v>
       </c>
       <c r="I109" t="n">
-        <v>0.9687</v>
+        <v>0.9224</v>
       </c>
       <c r="J109" t="n">
-        <v>19.374</v>
+        <v>18.448</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.32</v>
       </c>
       <c r="I110" t="n">
-        <v>0.7785</v>
+        <v>0.7514</v>
       </c>
       <c r="J110" t="n">
-        <v>15.57</v>
+        <v>15.028</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>1.14</v>
       </c>
       <c r="I111" t="n">
-        <v>0.3428</v>
+        <v>0.3623</v>
       </c>
       <c r="J111" t="n">
-        <v>6.856</v>
+        <v>7.246</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.04</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2302</v>
+        <v>0.2083</v>
       </c>
       <c r="J112" t="n">
-        <v>5.2946</v>
+        <v>4.7909</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>0.86</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1383</v>
+        <v>-0.1607</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.1809</v>
+        <v>-3.6961</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.57</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4196</v>
+        <v>-0.4342</v>
       </c>
       <c r="J114" t="n">
-        <v>-9.6508</v>
+        <v>-9.986599999999999</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.57</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4196</v>
+        <v>-0.4342</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.6508</v>
+        <v>-9.986599999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.53</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.457</v>
+        <v>-0.4695</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.511</v>
+        <v>-10.7985</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.64</v>
       </c>
       <c r="I117" t="n">
-        <v>1.2692</v>
+        <v>1.2494</v>
       </c>
       <c r="J117" t="n">
-        <v>29.1916</v>
+        <v>28.7362</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.6</v>
       </c>
       <c r="I118" t="n">
-        <v>1.2218</v>
+        <v>1.1988</v>
       </c>
       <c r="J118" t="n">
-        <v>28.1014</v>
+        <v>27.5724</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.51</v>
       </c>
       <c r="I119" t="n">
-        <v>1.1143</v>
+        <v>1.0829</v>
       </c>
       <c r="J119" t="n">
-        <v>25.6289</v>
+        <v>24.9067</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.34</v>
       </c>
       <c r="I120" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.8037</v>
       </c>
       <c r="J120" t="n">
-        <v>19.3706</v>
+        <v>18.4851</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.98</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1937</v>
+        <v>-0.1693</v>
       </c>
       <c r="J121" t="n">
-        <v>-4.4551</v>
+        <v>-3.8939</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>2.31</v>
       </c>
       <c r="I122" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J122" t="n">
-        <v>38.5098</v>
+        <v>40.6812</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.45</v>
       </c>
       <c r="I123" t="n">
-        <v>1.0396</v>
+        <v>0.997</v>
       </c>
       <c r="J123" t="n">
-        <v>21.8316</v>
+        <v>20.937</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.4</v>
       </c>
       <c r="I124" t="n">
-        <v>0.9634</v>
+        <v>0.9144</v>
       </c>
       <c r="J124" t="n">
-        <v>20.2314</v>
+        <v>19.2024</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.2</v>
       </c>
       <c r="I125" t="n">
-        <v>0.5145</v>
+        <v>0.5137</v>
       </c>
       <c r="J125" t="n">
-        <v>10.8045</v>
+        <v>10.7877</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.77</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7974</v>
+        <v>-0.7255</v>
       </c>
       <c r="J126" t="n">
-        <v>-16.7454</v>
+        <v>-15.2355</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.03</v>
       </c>
       <c r="I127" t="n">
-        <v>0.18</v>
+        <v>0.1645</v>
       </c>
       <c r="J127" t="n">
-        <v>3.78</v>
+        <v>3.4545</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>0.98</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0086</v>
+        <v>-0.0111</v>
       </c>
       <c r="J128" t="n">
-        <v>0.1806</v>
+        <v>-0.2331</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1578</v>
+        <v>-0.1783</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.3138</v>
+        <v>-3.7443</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.46</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.5278</v>
+        <v>-0.535</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.0838</v>
+        <v>-11.235</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.44</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5463</v>
+        <v>-0.5523</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.4723</v>
+        <v>-11.5983</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>2.04</v>
       </c>
       <c r="I132" t="n">
-        <v>1.718</v>
+        <v>1.724</v>
       </c>
       <c r="J132" t="n">
-        <v>39.514</v>
+        <v>39.652</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.65</v>
       </c>
       <c r="I133" t="n">
-        <v>1.274</v>
+        <v>1.2559</v>
       </c>
       <c r="J133" t="n">
-        <v>29.302</v>
+        <v>28.8857</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.58</v>
       </c>
       <c r="I134" t="n">
-        <v>1.192</v>
+        <v>1.1679</v>
       </c>
       <c r="J134" t="n">
-        <v>27.416</v>
+        <v>26.8617</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>1.21</v>
       </c>
       <c r="I135" t="n">
-        <v>0.5329</v>
+        <v>0.5314</v>
       </c>
       <c r="J135" t="n">
-        <v>12.2567</v>
+        <v>12.2222</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.8</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7272</v>
+        <v>-0.6622</v>
       </c>
       <c r="J136" t="n">
-        <v>-16.7256</v>
+        <v>-15.2306</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>0.85</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1365</v>
+        <v>-0.1616</v>
       </c>
       <c r="J137" t="n">
-        <v>-3.1395</v>
+        <v>-3.7168</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>0.78</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2132</v>
+        <v>-0.2367</v>
       </c>
       <c r="J138" t="n">
-        <v>-4.9036</v>
+        <v>-5.4441</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.66</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.329</v>
+        <v>-0.3491</v>
       </c>
       <c r="J139" t="n">
-        <v>-7.567</v>
+        <v>-8.029299999999999</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.66</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.329</v>
+        <v>-0.3491</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.567</v>
+        <v>-8.029299999999999</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.38</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5899</v>
+        <v>-0.5945</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.5677</v>
+        <v>-13.6735</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>1.2412</v>
+        <v>1.2089</v>
       </c>
       <c r="J142" t="n">
-        <v>37.236</v>
+        <v>36.267</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.28</v>
       </c>
       <c r="I143" t="n">
-        <v>0.758</v>
+        <v>0.7197</v>
       </c>
       <c r="J143" t="n">
-        <v>22.74</v>
+        <v>21.591</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.26</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7108</v>
+        <v>0.678</v>
       </c>
       <c r="J144" t="n">
-        <v>21.324</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.88</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4509</v>
+        <v>-0.4256</v>
       </c>
       <c r="J145" t="n">
-        <v>-13.527</v>
+        <v>-12.768</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.82</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6137</v>
+        <v>-0.5724</v>
       </c>
       <c r="J146" t="n">
-        <v>-18.411</v>
+        <v>-17.172</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.36</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7528</v>
+        <v>0.7147</v>
       </c>
       <c r="J147" t="n">
-        <v>22.584</v>
+        <v>21.441</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.1</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2667</v>
+        <v>0.2673</v>
       </c>
       <c r="J148" t="n">
-        <v>8.000999999999999</v>
+        <v>8.019</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>1.01</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0518</v>
+        <v>0.0534</v>
       </c>
       <c r="J149" t="n">
-        <v>1.554</v>
+        <v>1.602</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.64</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3845</v>
+        <v>-0.3957</v>
       </c>
       <c r="J150" t="n">
-        <v>-11.535</v>
+        <v>-11.871</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.54</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4764</v>
+        <v>-0.4834</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.292</v>
+        <v>-14.502</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.58</v>
       </c>
       <c r="I152" t="n">
-        <v>1.2105</v>
+        <v>1.1841</v>
       </c>
       <c r="J152" t="n">
-        <v>29.052</v>
+        <v>28.4184</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.53</v>
       </c>
       <c r="I153" t="n">
-        <v>1.1495</v>
+        <v>1.1187</v>
       </c>
       <c r="J153" t="n">
-        <v>27.588</v>
+        <v>26.8488</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>1.32</v>
       </c>
       <c r="I154" t="n">
-        <v>0.8109</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="J154" t="n">
-        <v>19.4616</v>
+        <v>18.5688</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>1.19</v>
       </c>
       <c r="I155" t="n">
-        <v>0.5077</v>
+        <v>0.504</v>
       </c>
       <c r="J155" t="n">
-        <v>12.1848</v>
+        <v>12.096</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>1.09</v>
       </c>
       <c r="I156" t="n">
-        <v>0.2408</v>
+        <v>0.2607</v>
       </c>
       <c r="J156" t="n">
-        <v>5.7792</v>
+        <v>6.2568</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>0.89</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.1107</v>
+        <v>-0.1316</v>
       </c>
       <c r="J157" t="n">
-        <v>-2.6568</v>
+        <v>-3.1584</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>0.88</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1223</v>
+        <v>-0.1432</v>
       </c>
       <c r="J158" t="n">
-        <v>-2.9352</v>
+        <v>-3.4368</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>0.83</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1772</v>
+        <v>-0.198</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.2528</v>
+        <v>-4.752</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.64</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3585</v>
+        <v>-0.3753</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.603999999999999</v>
+        <v>-9.007199999999999</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.47</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5171</v>
+        <v>-0.5252</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.4104</v>
+        <v>-12.6048</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.93</v>
       </c>
       <c r="I162" t="n">
-        <v>1.5921</v>
+        <v>1.5928</v>
       </c>
       <c r="J162" t="n">
-        <v>31.842</v>
+        <v>31.856</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.66</v>
       </c>
       <c r="I163" t="n">
-        <v>1.2838</v>
+        <v>1.2667</v>
       </c>
       <c r="J163" t="n">
-        <v>25.676</v>
+        <v>25.334</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.5</v>
       </c>
       <c r="I164" t="n">
-        <v>1.0964</v>
+        <v>1.0645</v>
       </c>
       <c r="J164" t="n">
-        <v>21.928</v>
+        <v>21.29</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>1.34</v>
       </c>
       <c r="I165" t="n">
-        <v>0.832</v>
+        <v>0.7967</v>
       </c>
       <c r="J165" t="n">
-        <v>16.64</v>
+        <v>15.934</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.91</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4324</v>
+        <v>-0.3941</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.648</v>
+        <v>-7.882</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1274</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="J167" t="n">
-        <v>2.548</v>
+        <v>1.866</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>0.77</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2259</v>
+        <v>-0.2487</v>
       </c>
       <c r="J168" t="n">
-        <v>-4.518</v>
+        <v>-4.974</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>0.65</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3392</v>
+        <v>-0.3587</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.784</v>
+        <v>-7.174</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.61</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.376</v>
+        <v>-0.3939</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.52</v>
+        <v>-7.878</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.35</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.6216</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.39</v>
+        <v>-12.432</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4328/event_4328_evp_summary.xlsx
+++ b/database/event/4328/event_4328_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.6165</v>
+        <v>4.5434</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0514</v>
+        <v>1.0348</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4773</v>
+        <v>1.4639</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6165</v>
+        <v>4.5434</v>
       </c>
       <c r="F2" t="n">
-        <v>2.592</v>
+        <v>2.5233</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0245</v>
+        <v>2.0201</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9481</v>
+        <v>2.8325</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9481</v>
+        <v>2.8325</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0245</v>
+        <v>2.0201</v>
       </c>
       <c r="K2" t="n">
         <v>127</v>
@@ -529,7 +529,7 @@
         <v>54</v>
       </c>
       <c r="M2" t="n">
-        <v>4.9726</v>
+        <v>4.8526</v>
       </c>
       <c r="N2" t="n">
         <v>181</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.1215</v>
+        <v>3.0025</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7109</v>
+        <v>0.6838</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7968</v>
+        <v>0.762</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1215</v>
+        <v>3.0025</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5981</v>
+        <v>2.5739</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5234</v>
+        <v>0.4286</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9616</v>
+        <v>2.9485</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9616</v>
+        <v>2.9485</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5234</v>
+        <v>0.4286</v>
       </c>
       <c r="K3" t="n">
         <v>132</v>
@@ -575,7 +575,7 @@
         <v>54</v>
       </c>
       <c r="M3" t="n">
-        <v>3.485</v>
+        <v>3.3771</v>
       </c>
       <c r="N3" t="n">
         <v>186</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.0545</v>
+        <v>2.9477</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6957</v>
+        <v>0.6714</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7663</v>
+        <v>0.737</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0545</v>
+        <v>2.9477</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5504</v>
+        <v>2.4854</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5041</v>
+        <v>0.4624</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8571</v>
+        <v>2.7456</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8571</v>
+        <v>2.7456</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5041</v>
+        <v>0.4624</v>
       </c>
       <c r="K4" t="n">
         <v>132</v>
@@ -621,7 +621,7 @@
         <v>54</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3612</v>
+        <v>3.208</v>
       </c>
       <c r="N4" t="n">
         <v>186</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.8727</v>
+        <v>2.773</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6543</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6835</v>
+        <v>0.6574</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8727</v>
+        <v>2.773</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8727</v>
+        <v>2.773</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5625</v>
+        <v>3.4047</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5625</v>
+        <v>3.4047</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5625</v>
+        <v>3.4047</v>
       </c>
       <c r="N5" t="n">
         <v>137</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.5275</v>
+        <v>2.5335</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5757</v>
+        <v>0.577</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5264</v>
+        <v>0.5483</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5275</v>
+        <v>2.5335</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1949</v>
+        <v>3.1686</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6674</v>
+        <v>-0.6351</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2676</v>
+        <v>4.3114</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2676</v>
+        <v>4.3114</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6674</v>
+        <v>-0.6351</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -713,7 +713,7 @@
         <v>54</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6002</v>
+        <v>3.6763</v>
       </c>
       <c r="N6" t="n">
         <v>186</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5096</v>
+        <v>2.4797</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5716</v>
+        <v>0.5648</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5182</v>
+        <v>0.5238</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5096</v>
+        <v>2.4797</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5096</v>
+        <v>2.4797</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7679</v>
+        <v>2.7326</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7679</v>
+        <v>2.7326</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7679</v>
+        <v>2.7326</v>
       </c>
       <c r="N7" t="n">
         <v>117</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.309</v>
+        <v>2.3228</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5259</v>
+        <v>0.529</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4269</v>
+        <v>0.4524</v>
       </c>
       <c r="E8" t="n">
-        <v>2.309</v>
+        <v>2.3228</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7576</v>
+        <v>1.765</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5514</v>
+        <v>0.5578</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7576</v>
+        <v>1.765</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7576</v>
+        <v>1.765</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5514</v>
+        <v>0.5578</v>
       </c>
       <c r="K8" t="n">
         <v>127</v>
@@ -805,7 +805,7 @@
         <v>54</v>
       </c>
       <c r="M8" t="n">
-        <v>2.309</v>
+        <v>2.3228</v>
       </c>
       <c r="N8" t="n">
         <v>181</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2539</v>
+        <v>2.2535</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5133</v>
+        <v>0.5132</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4018</v>
+        <v>0.4208</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2539</v>
+        <v>2.2535</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2539</v>
+        <v>2.2535</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2539</v>
+        <v>2.2535</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2539</v>
+        <v>2.2535</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2539</v>
+        <v>2.2535</v>
       </c>
       <c r="N9" t="n">
         <v>117</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1672</v>
+        <v>2.104</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4936</v>
+        <v>0.4792</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3624</v>
+        <v>0.3527</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1672</v>
+        <v>2.104</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1672</v>
+        <v>2.104</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1672</v>
+        <v>2.104</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1672</v>
+        <v>2.104</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1672</v>
+        <v>2.104</v>
       </c>
       <c r="N10" t="n">
         <v>120</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.9816</v>
+        <v>1.9619</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4513</v>
+        <v>0.4468</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2779</v>
+        <v>0.288</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9816</v>
+        <v>1.9619</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4084</v>
+        <v>2.3675</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4268</v>
+        <v>-0.4056</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5463</v>
+        <v>2.4754</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5463</v>
+        <v>2.4754</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4268</v>
+        <v>-0.4056</v>
       </c>
       <c r="K11" t="n">
         <v>127</v>
@@ -943,7 +943,7 @@
         <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1195</v>
+        <v>2.0698</v>
       </c>
       <c r="N11" t="n">
         <v>181</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7904</v>
+        <v>1.8581</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4078</v>
+        <v>0.4232</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1908</v>
+        <v>0.2407</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7904</v>
+        <v>1.8581</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7904</v>
+        <v>1.8581</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7904</v>
+        <v>1.8581</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7904</v>
+        <v>1.8581</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7904</v>
+        <v>1.8581</v>
       </c>
       <c r="N12" t="n">
         <v>120</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4728</v>
+        <v>1.3645</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3354</v>
+        <v>0.3108</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0462</v>
+        <v>0.0158</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4728</v>
+        <v>1.3645</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5523</v>
+        <v>0.5031</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9205</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5523</v>
+        <v>0.5031</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5523</v>
+        <v>0.5031</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9205</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>127</v>
@@ -1035,7 +1035,7 @@
         <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4728</v>
+        <v>1.3645</v>
       </c>
       <c r="N13" t="n">
         <v>181</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.426</v>
+        <v>1.3536</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3248</v>
+        <v>0.3083</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0249</v>
+        <v>0.0108</v>
       </c>
       <c r="E14" t="n">
-        <v>1.426</v>
+        <v>1.3536</v>
       </c>
       <c r="F14" t="n">
-        <v>1.426</v>
+        <v>1.3536</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.426</v>
+        <v>1.3536</v>
       </c>
       <c r="I14" t="n">
-        <v>1.426</v>
+        <v>1.3536</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.426</v>
+        <v>1.3536</v>
       </c>
       <c r="N14" t="n">
         <v>123</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.2443</v>
+        <v>1.2103</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2834</v>
+        <v>0.2757</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0578</v>
+        <v>-0.0544</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2443</v>
+        <v>1.2103</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2443</v>
+        <v>1.2103</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2443</v>
+        <v>1.2103</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2443</v>
+        <v>1.2103</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2443</v>
+        <v>1.2103</v>
       </c>
       <c r="N15" t="n">
         <v>120</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2198</v>
+        <v>1.2096</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2778</v>
+        <v>0.2755</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0689</v>
+        <v>-0.0548</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2198</v>
+        <v>1.2096</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2198</v>
+        <v>1.2096</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2198</v>
+        <v>1.2096</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2198</v>
+        <v>1.2096</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2198</v>
+        <v>1.2096</v>
       </c>
       <c r="N16" t="n">
         <v>117</v>
@@ -1182,47 +1182,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.11</v>
+        <v>1.0517</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2528</v>
+        <v>0.2395</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1189</v>
+        <v>-0.1267</v>
       </c>
       <c r="E17" t="n">
-        <v>1.11</v>
+        <v>1.0517</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8858</v>
+        <v>1.7947</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2242</v>
+        <v>-0.743</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8858</v>
+        <v>1.7947</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8858</v>
+        <v>1.7947</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2242</v>
+        <v>-0.743</v>
       </c>
       <c r="K17" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="L17" t="n">
         <v>54</v>
       </c>
       <c r="M17" t="n">
-        <v>1.11</v>
+        <v>1.0517</v>
       </c>
       <c r="N17" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0183</v>
+        <v>1.0275</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2319</v>
+        <v>0.234</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1607</v>
+        <v>-0.1377</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0183</v>
+        <v>1.0275</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0183</v>
+        <v>1.0275</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0183</v>
+        <v>1.0275</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0183</v>
+        <v>1.0275</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0183</v>
+        <v>1.0275</v>
       </c>
       <c r="N18" t="n">
         <v>117</v>
@@ -1274,139 +1274,139 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0033</v>
+        <v>1.0204</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2285</v>
+        <v>0.2324</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1675</v>
+        <v>-0.1409</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0033</v>
+        <v>1.0204</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7704</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7671</v>
+        <v>0.1782</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7704</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7704</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7671</v>
+        <v>0.1782</v>
       </c>
       <c r="K19" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="L19" t="n">
         <v>54</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0033</v>
+        <v>1.0204</v>
       </c>
       <c r="N19" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>MUTiRiS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7331</v>
+        <v>0.7517</v>
       </c>
       <c r="C20" t="n">
-        <v>0.167</v>
+        <v>0.1712</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2905</v>
+        <v>-0.2634</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7331</v>
+        <v>0.7517</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7331</v>
+        <v>0.7517</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7331</v>
+        <v>0.7517</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7331</v>
+        <v>0.7517</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7331</v>
+        <v>0.7517</v>
       </c>
       <c r="N20" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MUTiRiS</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6575</v>
+        <v>0.7443</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1497</v>
+        <v>0.1695</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3249</v>
+        <v>-0.2667</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6575</v>
+        <v>0.7443</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6575</v>
+        <v>0.7443</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6575</v>
+        <v>0.7443</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6575</v>
+        <v>0.7443</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6575</v>
+        <v>0.7443</v>
       </c>
       <c r="N21" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1707</v>
+        <v>0.2037</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0389</v>
+        <v>0.0464</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5465</v>
+        <v>-0.513</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1707</v>
+        <v>0.2037</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1707</v>
+        <v>0.2037</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1707</v>
+        <v>0.2037</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1707</v>
+        <v>0.2037</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1707</v>
+        <v>0.2037</v>
       </c>
       <c r="N22" t="n">
         <v>123</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1127</v>
+        <v>0.0838</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0257</v>
+        <v>0.0191</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5729</v>
+        <v>-0.5676</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1127</v>
+        <v>0.0838</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1127</v>
+        <v>0.1596</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1127</v>
+        <v>0.1596</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1127</v>
+        <v>0.1596</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1127</v>
+        <v>0.08379999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>123</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0152</v>
+        <v>0.0023</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5939</v>
+        <v>-0.6012</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1417</v>
+        <v>0.01</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0751</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1417</v>
+        <v>0.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1417</v>
+        <v>0.01</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0751</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="L24" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.06659999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="N24" t="n">
-        <v>186</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1633</v>
+        <v>-0.1239</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0372</v>
+        <v>-0.0282</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6985</v>
+        <v>-0.6622</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1633</v>
+        <v>-0.1239</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1633</v>
+        <v>-0.1239</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1633</v>
+        <v>-0.1239</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1633</v>
+        <v>-0.1239</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1633</v>
+        <v>-0.1239</v>
       </c>
       <c r="N25" t="n">
         <v>137</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.177</v>
+        <v>-0.1706</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0403</v>
+        <v>-0.0389</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7048</v>
+        <v>-0.6835</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.177</v>
+        <v>-0.1706</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.177</v>
+        <v>-0.1706</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.177</v>
+        <v>-0.1706</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.177</v>
+        <v>-0.1706</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.177</v>
+        <v>-0.1706</v>
       </c>
       <c r="N26" t="n">
         <v>120</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3048</v>
+        <v>-0.293</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0694</v>
+        <v>-0.0667</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.763</v>
+        <v>-0.7393</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3048</v>
+        <v>-0.293</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3048</v>
+        <v>-0.293</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3048</v>
+        <v>-0.293</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3048</v>
+        <v>-0.293</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3048</v>
+        <v>-0.293</v>
       </c>
       <c r="N27" t="n">
         <v>137</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.5726</v>
+        <v>-0.6278</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1304</v>
+        <v>-0.143</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8849</v>
+        <v>-0.8918</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5726</v>
+        <v>-0.6278</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.5726</v>
+        <v>-0.6278</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.5726</v>
+        <v>-0.6278</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5726</v>
+        <v>-0.6278</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.5726</v>
+        <v>-0.6278</v>
       </c>
       <c r="N28" t="n">
         <v>123</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.333</v>
+        <v>-1.2992</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3036</v>
+        <v>-0.2959</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.231</v>
+        <v>-1.1976</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.333</v>
+        <v>-1.2992</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.333</v>
+        <v>-1.2992</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.333</v>
+        <v>-1.2992</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.333</v>
+        <v>-1.2992</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.333</v>
+        <v>-1.2992</v>
       </c>
       <c r="N29" t="n">
         <v>120</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.5755</v>
+        <v>-1.4779</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3588</v>
+        <v>-0.3366</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.3414</v>
+        <v>-1.279</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.5755</v>
+        <v>-1.4779</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.5755</v>
+        <v>-1.4779</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.5755</v>
+        <v>-1.4779</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.5755</v>
+        <v>-1.4779</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.5755</v>
+        <v>-1.4779</v>
       </c>
       <c r="N30" t="n">
         <v>137</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.3064</v>
+        <v>-2.2396</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.5253</v>
+        <v>-0.5101</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.6741</v>
+        <v>-1.626</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.3064</v>
+        <v>-2.2396</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.3064</v>
+        <v>-2.2396</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.3064</v>
+        <v>-2.2396</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.3064</v>
+        <v>-2.2396</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.3064</v>
+        <v>-2.2396</v>
       </c>
       <c r="N31" t="n">
         <v>137</v>
@@ -1969,10 +1969,10 @@
         <v>1.06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2057</v>
+        <v>0.1658</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1425</v>
+        <v>4.145</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>0.91</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1232</v>
+        <v>-0.1079</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.08</v>
+        <v>-2.6975</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.87</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1679</v>
+        <v>-0.1507</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.1975</v>
+        <v>-3.7675</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.7</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3324</v>
+        <v>-0.3161</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.31</v>
+        <v>-7.9025</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.68</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3507</v>
+        <v>-0.3356</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.7675</v>
+        <v>-8.390000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.59</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2906</v>
+        <v>1.3175</v>
       </c>
       <c r="J7" t="n">
-        <v>32.265</v>
+        <v>32.9375</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.29</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7254</v>
+        <v>0.699</v>
       </c>
       <c r="J8" t="n">
-        <v>18.135</v>
+        <v>17.475</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>1.29</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7254</v>
+        <v>0.699</v>
       </c>
       <c r="J9" t="n">
-        <v>18.135</v>
+        <v>17.475</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>1.03</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0762</v>
       </c>
       <c r="J10" t="n">
-        <v>2.415</v>
+        <v>1.905</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>1.02</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0601</v>
+        <v>0.0438</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5025</v>
+        <v>1.095</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.34</v>
       </c>
       <c r="I12" t="n">
-        <v>0.672</v>
+        <v>0.6163</v>
       </c>
       <c r="J12" t="n">
-        <v>19.488</v>
+        <v>17.8727</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3177</v>
+        <v>0.2658</v>
       </c>
       <c r="J13" t="n">
-        <v>9.2133</v>
+        <v>7.7082</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0481</v>
+        <v>0.0321</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3949</v>
+        <v>0.9308999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.71</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.335</v>
+        <v>-0.319</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.715</v>
+        <v>-9.250999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.62</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4164</v>
+        <v>-0.4074</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.0756</v>
+        <v>-11.8146</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.27</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7339</v>
+        <v>0.7026</v>
       </c>
       <c r="J17" t="n">
-        <v>21.2831</v>
+        <v>20.3754</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1951</v>
+        <v>0.1624</v>
       </c>
       <c r="J18" t="n">
-        <v>5.6579</v>
+        <v>4.7096</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1641</v>
+        <v>0.1344</v>
       </c>
       <c r="J19" t="n">
-        <v>4.7589</v>
+        <v>3.8976</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.174</v>
+        <v>-0.1412</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.046</v>
+        <v>-4.0948</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5234</v>
+        <v>-0.4818</v>
       </c>
       <c r="J21" t="n">
-        <v>-15.1786</v>
+        <v>-13.9722</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.28</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7227</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>21.681</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.24</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6385</v>
+        <v>0.604</v>
       </c>
       <c r="J23" t="n">
-        <v>19.155</v>
+        <v>18.12</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.22</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5955</v>
+        <v>0.5596</v>
       </c>
       <c r="J24" t="n">
-        <v>17.865</v>
+        <v>16.788</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.13</v>
       </c>
       <c r="I25" t="n">
-        <v>0.393</v>
+        <v>0.3565</v>
       </c>
       <c r="J25" t="n">
-        <v>11.79</v>
+        <v>10.695</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4484</v>
+        <v>-0.4067</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.452</v>
+        <v>-12.201</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.06</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1782</v>
+        <v>0.1393</v>
       </c>
       <c r="J27" t="n">
-        <v>5.346</v>
+        <v>4.179</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1556</v>
+        <v>0.1197</v>
       </c>
       <c r="J28" t="n">
-        <v>4.668</v>
+        <v>3.591</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0226</v>
+        <v>-0.0167</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.678</v>
+        <v>-0.501</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.92</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.12</v>
+        <v>-0.1024</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.6</v>
+        <v>-3.072</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2967</v>
+        <v>-0.2784</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.901</v>
+        <v>-8.352</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.49</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0724</v>
+        <v>1.082</v>
       </c>
       <c r="J32" t="n">
-        <v>28.9548</v>
+        <v>29.214</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.7768</v>
       </c>
       <c r="J33" t="n">
-        <v>21.5163</v>
+        <v>20.9736</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1.28</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7004</v>
+        <v>0.6756</v>
       </c>
       <c r="J34" t="n">
-        <v>18.9108</v>
+        <v>18.2412</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>1.28</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7004</v>
+        <v>0.6756</v>
       </c>
       <c r="J35" t="n">
-        <v>18.9108</v>
+        <v>18.2412</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>1.1</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2946</v>
+        <v>0.2631</v>
       </c>
       <c r="J36" t="n">
-        <v>7.9542</v>
+        <v>7.1037</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7912</v>
+        <v>0.7644</v>
       </c>
       <c r="J37" t="n">
-        <v>21.3624</v>
+        <v>20.6388</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>0.79</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.242</v>
+        <v>-0.2253</v>
       </c>
       <c r="J38" t="n">
-        <v>-6.534</v>
+        <v>-6.0831</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>0.62</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3971</v>
+        <v>-0.3854</v>
       </c>
       <c r="J39" t="n">
-        <v>-10.7217</v>
+        <v>-10.4058</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>0.61</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.406</v>
+        <v>-0.395</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.962</v>
+        <v>-10.665</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.49</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5115</v>
+        <v>-0.5118</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.8105</v>
+        <v>-13.8186</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.19</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5372</v>
+        <v>0.4982</v>
       </c>
       <c r="J42" t="n">
-        <v>13.43</v>
+        <v>12.455</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4684</v>
+        <v>0.4289</v>
       </c>
       <c r="J43" t="n">
-        <v>11.71</v>
+        <v>10.7225</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.09</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2981</v>
+        <v>0.2624</v>
       </c>
       <c r="J44" t="n">
-        <v>7.4525</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>1.06</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2152</v>
+        <v>0.1844</v>
       </c>
       <c r="J45" t="n">
-        <v>5.38</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>1.03</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1205</v>
+        <v>0.0983</v>
       </c>
       <c r="J46" t="n">
-        <v>3.0125</v>
+        <v>2.4575</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.01</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0466</v>
+        <v>0.0312</v>
       </c>
       <c r="J47" t="n">
-        <v>1.165</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0027</v>
+        <v>0.0013</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0675</v>
+        <v>0.0325</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>0.97</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0566</v>
+        <v>-0.0448</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.415</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0969</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.4225</v>
+        <v>-2.0175</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0969</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.4225</v>
+        <v>-2.0175</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.3</v>
       </c>
       <c r="I52" t="n">
-        <v>0.61</v>
+        <v>0.5527</v>
       </c>
       <c r="J52" t="n">
-        <v>18.3</v>
+        <v>16.581</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>0.96</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0701</v>
+        <v>-0.0569</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.103</v>
+        <v>-1.707</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0959</v>
+        <v>-0.0801</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.877</v>
+        <v>-2.403</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.87</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1765</v>
+        <v>-0.1564</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.295</v>
+        <v>-4.692</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.72</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3253</v>
+        <v>-0.3087</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.759</v>
+        <v>-9.260999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.45</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0488</v>
+        <v>1.0543</v>
       </c>
       <c r="J57" t="n">
-        <v>31.464</v>
+        <v>31.629</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.37</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9095</v>
+        <v>0.8923</v>
       </c>
       <c r="J58" t="n">
-        <v>27.285</v>
+        <v>26.769</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.99</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.0605</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.436</v>
+        <v>-1.815</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.96</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.193</v>
+        <v>-0.1584</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.79</v>
+        <v>-4.752</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.89</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3942</v>
+        <v>-0.3518</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.826</v>
+        <v>-10.554</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.47</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8623</v>
+        <v>0.8162</v>
       </c>
       <c r="J62" t="n">
-        <v>25.0067</v>
+        <v>23.6698</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.06</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1734</v>
+        <v>0.1354</v>
       </c>
       <c r="J63" t="n">
-        <v>5.0286</v>
+        <v>3.9266</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.87</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1784</v>
+        <v>-0.1581</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.1736</v>
+        <v>-4.5849</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2406</v>
+        <v>-0.2204</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.9774</v>
+        <v>-6.3916</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3551</v>
+        <v>-0.3407</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.2979</v>
+        <v>-9.8803</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.18</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5119</v>
+        <v>0.4732</v>
       </c>
       <c r="J67" t="n">
-        <v>14.8451</v>
+        <v>13.7228</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.17</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4891</v>
+        <v>0.4503</v>
       </c>
       <c r="J68" t="n">
-        <v>14.1839</v>
+        <v>13.0587</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.14</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4194</v>
+        <v>0.3809</v>
       </c>
       <c r="J69" t="n">
-        <v>12.1626</v>
+        <v>11.0461</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.07</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2418</v>
+        <v>0.2097</v>
       </c>
       <c r="J70" t="n">
-        <v>7.0122</v>
+        <v>6.0813</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>1.04</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1516</v>
+        <v>0.1264</v>
       </c>
       <c r="J71" t="n">
-        <v>4.3964</v>
+        <v>3.6656</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.83</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4722</v>
+        <v>1.5019</v>
       </c>
       <c r="J72" t="n">
-        <v>29.444</v>
+        <v>30.038</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.72</v>
       </c>
       <c r="I73" t="n">
-        <v>1.3392</v>
+        <v>1.3618</v>
       </c>
       <c r="J73" t="n">
-        <v>26.784</v>
+        <v>27.236</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.4</v>
       </c>
       <c r="I74" t="n">
-        <v>0.9087</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>18.174</v>
+        <v>18.094</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.26</v>
       </c>
       <c r="I75" t="n">
-        <v>0.635</v>
+        <v>0.6125</v>
       </c>
       <c r="J75" t="n">
-        <v>12.7</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.18</v>
       </c>
       <c r="I76" t="n">
-        <v>0.4612</v>
+        <v>0.4308</v>
       </c>
       <c r="J76" t="n">
-        <v>9.224</v>
+        <v>8.616</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.07</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3316</v>
+        <v>0.3148</v>
       </c>
       <c r="J77" t="n">
-        <v>6.632</v>
+        <v>6.296</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>0.58</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.4145</v>
+        <v>-0.406</v>
       </c>
       <c r="J78" t="n">
-        <v>-8.289999999999999</v>
+        <v>-8.119999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.58</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4145</v>
+        <v>-0.406</v>
       </c>
       <c r="J79" t="n">
-        <v>-8.289999999999999</v>
+        <v>-8.119999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.53</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4584</v>
+        <v>-0.4526</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.167999999999999</v>
+        <v>-9.052</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.4</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5727</v>
+        <v>-0.5802</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.454</v>
+        <v>-11.604</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.35</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.8827</v>
       </c>
       <c r="J82" t="n">
-        <v>26.0913</v>
+        <v>25.5983</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.11</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3595</v>
+        <v>0.3183</v>
       </c>
       <c r="J83" t="n">
-        <v>10.4255</v>
+        <v>9.230700000000001</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>0.97</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1419</v>
+        <v>-0.1123</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.1151</v>
+        <v>-3.2567</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.88</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4017</v>
+        <v>-0.3586</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.6493</v>
+        <v>-10.3994</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.88</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4017</v>
+        <v>-0.3586</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.6493</v>
+        <v>-10.3994</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.33</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6354</v>
+        <v>0.5764</v>
       </c>
       <c r="J87" t="n">
-        <v>18.4266</v>
+        <v>16.7156</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.29</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5134</v>
       </c>
       <c r="J88" t="n">
-        <v>16.6199</v>
+        <v>14.8886</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>1.05</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1439</v>
+        <v>0.1114</v>
       </c>
       <c r="J89" t="n">
-        <v>4.1731</v>
+        <v>3.2306</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.84</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2148</v>
+        <v>-0.1942</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.2292</v>
+        <v>-5.6318</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.65</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3957</v>
+        <v>-0.3854</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.4753</v>
+        <v>-11.1766</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7441</v>
+        <v>0.6966</v>
       </c>
       <c r="J92" t="n">
-        <v>20.0907</v>
+        <v>18.8082</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>0.95</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0789</v>
+        <v>-0.066</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.1303</v>
+        <v>-1.782</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.82</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2227</v>
+        <v>-0.2029</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.0129</v>
+        <v>-5.4783</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.78</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2621</v>
+        <v>-0.2428</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.0767</v>
+        <v>-6.5556</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.463</v>
+        <v>-0.4586</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.501</v>
+        <v>-12.3822</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.32</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8079</v>
+        <v>0.7823</v>
       </c>
       <c r="J97" t="n">
-        <v>21.8133</v>
+        <v>21.1221</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.27</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7045</v>
+        <v>0.6725</v>
       </c>
       <c r="J98" t="n">
-        <v>19.0215</v>
+        <v>18.1575</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.09</v>
       </c>
       <c r="I99" t="n">
-        <v>0.294</v>
+        <v>0.2599</v>
       </c>
       <c r="J99" t="n">
-        <v>7.938</v>
+        <v>7.0173</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.06</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2104</v>
+        <v>0.1808</v>
       </c>
       <c r="J100" t="n">
-        <v>5.6808</v>
+        <v>4.8816</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2562</v>
+        <v>-0.2173</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.9174</v>
+        <v>-5.8671</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.02</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1814</v>
+        <v>0.1685</v>
       </c>
       <c r="J102" t="n">
-        <v>3.628</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>0.87</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1372</v>
+        <v>-0.1198</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.744</v>
+        <v>-2.396</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.58</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.4183</v>
+        <v>-0.4092</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.366</v>
+        <v>-8.183999999999999</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.43</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5501</v>
+        <v>-0.5546</v>
       </c>
       <c r="J105" t="n">
-        <v>-11.002</v>
+        <v>-11.092</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.4</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5763</v>
+        <v>-0.5847</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.526</v>
+        <v>-11.694</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>2.25</v>
       </c>
       <c r="I107" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J107" t="n">
-        <v>38.744</v>
+        <v>39.636</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.45</v>
       </c>
       <c r="I108" t="n">
-        <v>0.9901</v>
+        <v>0.9973</v>
       </c>
       <c r="J108" t="n">
-        <v>19.802</v>
+        <v>19.946</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.41</v>
       </c>
       <c r="I109" t="n">
-        <v>0.9224</v>
+        <v>0.9212</v>
       </c>
       <c r="J109" t="n">
-        <v>18.448</v>
+        <v>18.424</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.32</v>
       </c>
       <c r="I110" t="n">
-        <v>0.7514</v>
+        <v>0.7368</v>
       </c>
       <c r="J110" t="n">
-        <v>15.028</v>
+        <v>14.736</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>1.14</v>
       </c>
       <c r="I111" t="n">
-        <v>0.3623</v>
+        <v>0.329</v>
       </c>
       <c r="J111" t="n">
-        <v>7.246</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.04</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2083</v>
+        <v>0.1811</v>
       </c>
       <c r="J112" t="n">
-        <v>4.7909</v>
+        <v>4.1653</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>0.86</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1607</v>
+        <v>-0.145</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.6961</v>
+        <v>-3.335</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.57</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4342</v>
+        <v>-0.4257</v>
       </c>
       <c r="J114" t="n">
-        <v>-9.986599999999999</v>
+        <v>-9.7911</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.57</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4342</v>
+        <v>-0.4257</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.986599999999999</v>
+        <v>-9.7911</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.53</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4695</v>
+        <v>-0.4644</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.7985</v>
+        <v>-10.6812</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.64</v>
       </c>
       <c r="I117" t="n">
-        <v>1.2494</v>
+        <v>1.2675</v>
       </c>
       <c r="J117" t="n">
-        <v>28.7362</v>
+        <v>29.1525</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.6</v>
       </c>
       <c r="I118" t="n">
-        <v>1.1988</v>
+        <v>1.2154</v>
       </c>
       <c r="J118" t="n">
-        <v>27.5724</v>
+        <v>27.9542</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.51</v>
       </c>
       <c r="I119" t="n">
-        <v>1.0829</v>
+        <v>1.0967</v>
       </c>
       <c r="J119" t="n">
-        <v>24.9067</v>
+        <v>25.2241</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.34</v>
       </c>
       <c r="I120" t="n">
-        <v>0.8037</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="J120" t="n">
-        <v>18.4851</v>
+        <v>18.1654</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.98</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1693</v>
+        <v>-0.1463</v>
       </c>
       <c r="J121" t="n">
-        <v>-3.8939</v>
+        <v>-3.3649</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>2.31</v>
       </c>
       <c r="I122" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J122" t="n">
-        <v>40.6812</v>
+        <v>41.6178</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.45</v>
       </c>
       <c r="I123" t="n">
-        <v>0.997</v>
+        <v>1.0013</v>
       </c>
       <c r="J123" t="n">
-        <v>20.937</v>
+        <v>21.0273</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.4</v>
       </c>
       <c r="I124" t="n">
-        <v>0.9144</v>
+        <v>0.9086</v>
       </c>
       <c r="J124" t="n">
-        <v>19.2024</v>
+        <v>19.0806</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.2</v>
       </c>
       <c r="I125" t="n">
-        <v>0.5137</v>
+        <v>0.4852</v>
       </c>
       <c r="J125" t="n">
-        <v>10.7877</v>
+        <v>10.1892</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.77</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7255</v>
+        <v>-0.7054</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.2355</v>
+        <v>-14.8134</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.03</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1645</v>
+        <v>0.1371</v>
       </c>
       <c r="J127" t="n">
-        <v>3.4545</v>
+        <v>2.8791</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>0.98</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0111</v>
+        <v>-0.0024</v>
       </c>
       <c r="J128" t="n">
-        <v>-0.2331</v>
+        <v>-0.0504</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1783</v>
+        <v>-0.1626</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.7443</v>
+        <v>-3.4146</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.46</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.535</v>
+        <v>-0.5384</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.235</v>
+        <v>-11.3064</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.44</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5523</v>
+        <v>-0.5581</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.5983</v>
+        <v>-11.7201</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>2.04</v>
       </c>
       <c r="I132" t="n">
-        <v>1.724</v>
+        <v>1.7745</v>
       </c>
       <c r="J132" t="n">
-        <v>39.652</v>
+        <v>40.8135</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.65</v>
       </c>
       <c r="I133" t="n">
-        <v>1.2559</v>
+        <v>1.275</v>
       </c>
       <c r="J133" t="n">
-        <v>28.8857</v>
+        <v>29.325</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.58</v>
       </c>
       <c r="I134" t="n">
-        <v>1.1679</v>
+        <v>1.185</v>
       </c>
       <c r="J134" t="n">
-        <v>26.8617</v>
+        <v>27.255</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>1.21</v>
       </c>
       <c r="I135" t="n">
-        <v>0.5314</v>
+        <v>0.5037</v>
       </c>
       <c r="J135" t="n">
-        <v>12.2222</v>
+        <v>11.5851</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.8</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6622</v>
+        <v>-0.6384</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.2306</v>
+        <v>-14.6832</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>0.85</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1616</v>
+        <v>-0.1451</v>
       </c>
       <c r="J137" t="n">
-        <v>-3.7168</v>
+        <v>-3.3373</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>0.78</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2367</v>
+        <v>-0.2224</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.4441</v>
+        <v>-5.1152</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.66</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3491</v>
+        <v>-0.3373</v>
       </c>
       <c r="J139" t="n">
-        <v>-8.029299999999999</v>
+        <v>-7.7579</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.66</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3491</v>
+        <v>-0.3373</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.029299999999999</v>
+        <v>-7.7579</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.38</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5945</v>
+        <v>-0.6058</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.6735</v>
+        <v>-13.9334</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>1.2089</v>
+        <v>1.2251</v>
       </c>
       <c r="J142" t="n">
-        <v>36.267</v>
+        <v>36.753</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.28</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7197</v>
+        <v>0.6893</v>
       </c>
       <c r="J143" t="n">
-        <v>21.591</v>
+        <v>20.679</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.26</v>
       </c>
       <c r="I144" t="n">
-        <v>0.678</v>
+        <v>0.6456</v>
       </c>
       <c r="J144" t="n">
-        <v>20.34</v>
+        <v>19.368</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.88</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4256</v>
+        <v>-0.3838</v>
       </c>
       <c r="J145" t="n">
-        <v>-12.768</v>
+        <v>-11.514</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.82</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5724</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="J146" t="n">
-        <v>-17.172</v>
+        <v>-16.044</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.36</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7147</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="J147" t="n">
-        <v>21.441</v>
+        <v>19.884</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.1</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2673</v>
+        <v>0.2192</v>
       </c>
       <c r="J148" t="n">
-        <v>8.019</v>
+        <v>6.576</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>1.01</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0534</v>
+        <v>0.0361</v>
       </c>
       <c r="J149" t="n">
-        <v>1.602</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.64</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3957</v>
+        <v>-0.3844</v>
       </c>
       <c r="J150" t="n">
-        <v>-11.871</v>
+        <v>-11.532</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.54</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4834</v>
+        <v>-0.4819</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.502</v>
+        <v>-14.457</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.58</v>
       </c>
       <c r="I152" t="n">
-        <v>1.1841</v>
+        <v>1.199</v>
       </c>
       <c r="J152" t="n">
-        <v>28.4184</v>
+        <v>28.776</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.53</v>
       </c>
       <c r="I153" t="n">
-        <v>1.1187</v>
+        <v>1.1321</v>
       </c>
       <c r="J153" t="n">
-        <v>26.8488</v>
+        <v>27.1704</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>1.32</v>
       </c>
       <c r="I154" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.7547</v>
       </c>
       <c r="J154" t="n">
-        <v>18.5688</v>
+        <v>18.1128</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>1.19</v>
       </c>
       <c r="I155" t="n">
-        <v>0.504</v>
+        <v>0.4742</v>
       </c>
       <c r="J155" t="n">
-        <v>12.096</v>
+        <v>11.3808</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>1.09</v>
       </c>
       <c r="I156" t="n">
-        <v>0.2607</v>
+        <v>0.2295</v>
       </c>
       <c r="J156" t="n">
-        <v>6.2568</v>
+        <v>5.508</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>0.89</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.1316</v>
+        <v>-0.1163</v>
       </c>
       <c r="J157" t="n">
-        <v>-3.1584</v>
+        <v>-2.7912</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>0.88</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1432</v>
+        <v>-0.1278</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.4368</v>
+        <v>-3.0672</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>0.83</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.198</v>
+        <v>-0.1824</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.752</v>
+        <v>-4.3776</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.64</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3753</v>
+        <v>-0.3624</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.007199999999999</v>
+        <v>-8.6976</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.47</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5252</v>
+        <v>-0.5271</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.6048</v>
+        <v>-12.6504</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.93</v>
       </c>
       <c r="I162" t="n">
-        <v>1.5928</v>
+        <v>1.6313</v>
       </c>
       <c r="J162" t="n">
-        <v>31.856</v>
+        <v>32.626</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.66</v>
       </c>
       <c r="I163" t="n">
-        <v>1.2667</v>
+        <v>1.2864</v>
       </c>
       <c r="J163" t="n">
-        <v>25.334</v>
+        <v>25.728</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.5</v>
       </c>
       <c r="I164" t="n">
-        <v>1.0645</v>
+        <v>1.0788</v>
       </c>
       <c r="J164" t="n">
-        <v>21.29</v>
+        <v>21.576</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>1.34</v>
       </c>
       <c r="I165" t="n">
-        <v>0.7967</v>
+        <v>0.7842</v>
       </c>
       <c r="J165" t="n">
-        <v>15.934</v>
+        <v>15.684</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.91</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3941</v>
+        <v>-0.3613</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.882</v>
+        <v>-7.226</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1</v>
       </c>
       <c r="I167" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.096</v>
       </c>
       <c r="J167" t="n">
-        <v>1.866</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>0.77</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2487</v>
+        <v>-0.2346</v>
       </c>
       <c r="J168" t="n">
-        <v>-4.974</v>
+        <v>-4.692</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>0.65</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3587</v>
+        <v>-0.3466</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.174</v>
+        <v>-6.932</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.61</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3939</v>
+        <v>-0.3831</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.878</v>
+        <v>-7.662</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.35</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6216</v>
+        <v>-0.6377</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.432</v>
+        <v>-12.754</v>
       </c>
     </row>
   </sheetData>
